--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -58,6 +58,15 @@
     <t>sale</t>
   </si>
   <si>
+    <t>made</t>
+  </si>
+  <si>
+    <t>broken</t>
+  </si>
+  <si>
+    <t>added</t>
+  </si>
+  <si>
     <t>提升属性一8点</t>
   </si>
   <si>
@@ -97,25 +106,25 @@
     <t>提升属性一30点，减少属性二10点，属性二减少的数值不会改变</t>
   </si>
   <si>
-    <t>提升仙台同学的属性一8，当此牌被拆卸时，不会被消耗</t>
-  </si>
-  <si>
-    <t>提升仙台同学的属性二16，当此牌被手工时，往手牌中额外加入一张此卡</t>
-  </si>
-  <si>
-    <t>提升属性二14点，被手工时，提升属性二4点</t>
-  </si>
-  <si>
-    <t>提升属性一12点，被美化时，获得xx金币</t>
+    <t>提升仙台同学的属性一8，当此牌被剪枝时，不会被消耗</t>
+  </si>
+  <si>
+    <t>提升仙台同学的属性二16，当此牌被生枝时，往手牌中额外加入一张此卡</t>
+  </si>
+  <si>
+    <t>提升属性二14点，被生枝时，提升属性二4点</t>
+  </si>
+  <si>
+    <t>提升属性一12点，被生长时，获得xx金币</t>
   </si>
   <si>
     <t>提升属性一40点，下回合好感度加成减少50%</t>
   </si>
   <si>
-    <t>提升属性二10点，被拆卸时，提升属性三10点</t>
-  </si>
-  <si>
-    <t>提升属性一1点，属性二1点，被美化时，额外被美化1次</t>
+    <t>提升属性二10点，被剪枝时，提升属性三10点</t>
+  </si>
+  <si>
+    <t>提升属性一1点，属性二1点，被生长时，额外被生长1次</t>
   </si>
   <si>
     <t>让属性一的数值等于属性二</t>
@@ -131,7 +140,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,137 +620,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -742,13 +758,16 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1101,9 +1120,15 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
@@ -1126,8 +1151,11 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -1143,7 +1171,10 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3">
         <v>10</v>
       </c>
     </row>
@@ -1160,8 +1191,11 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:20">
@@ -1169,7 +1203,7 @@
         <v>11004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1180,8 +1214,11 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1189,7 +1226,7 @@
         <v>11005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -1200,8 +1237,11 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>15</v>
+      <c r="F6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1209,7 +1249,7 @@
         <v>11006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1220,8 +1260,11 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1237,8 +1280,11 @@
       <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>18</v>
+      <c r="F8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1254,8 +1300,11 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>19</v>
+      <c r="F9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1271,7 +1320,10 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10">
         <v>20</v>
       </c>
     </row>
@@ -1288,8 +1340,11 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>21</v>
+      <c r="F11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1305,8 +1360,11 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>22</v>
+      <c r="F12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12">
+        <v>20</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:20">
@@ -1322,8 +1380,11 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>23</v>
+      <c r="F13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1339,8 +1400,11 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>24</v>
+      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1356,8 +1420,11 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>25</v>
+      <c r="F15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15">
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1373,11 +1440,14 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="F16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>12010</v>
       </c>
@@ -1390,11 +1460,14 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="F17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>12011</v>
       </c>
@@ -1407,11 +1480,14 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="F18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>13001</v>
       </c>
@@ -1424,8 +1500,11 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>29</v>
+      <c r="F19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>提升属性一8点</t>
+  </si>
+  <si>
+    <t>p("aaa")</t>
   </si>
   <si>
     <t>提升仙台同学的属性二12点</t>
@@ -1129,6 +1132,9 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3">
@@ -1144,6 +1150,9 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1161,7 +1170,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="28" spans="1:20">
@@ -1169,7 +1181,7 @@
         <v>11004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1181,7 +1193,10 @@
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -1189,7 +1204,7 @@
         <v>11005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -1201,7 +1216,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1209,7 +1227,7 @@
         <v>11006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1221,7 +1239,10 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1238,7 +1259,10 @@
         <v>2</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1255,7 +1279,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1272,7 +1299,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1289,7 +1319,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1306,7 +1339,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:20">
@@ -1323,7 +1359,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1340,7 +1379,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1357,7 +1399,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1374,10 +1419,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>27</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>12010</v>
       </c>
@@ -1391,10 +1439,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>12011</v>
       </c>
@@ -1408,10 +1459,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>29</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>13001</v>
       </c>
@@ -1425,7 +1479,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -67,67 +67,94 @@
     <t>added</t>
   </si>
   <si>
-    <t>提升属性一8点</t>
-  </si>
-  <si>
-    <t>提升仙台同学的属性二12点</t>
-  </si>
-  <si>
-    <t>提升属性一2点，属性二2点</t>
+    <t>nextTurn</t>
+  </si>
+  <si>
+    <t>提升角色的属性一{nature1}点</t>
+  </si>
+  <si>
+    <t>提升角色的属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>提升角色的属性一{nature1}点，属性二{nature2}点</t>
   </si>
   <si>
     <t>雪莉牌手榨苹果汁</t>
   </si>
   <si>
-    <t>提升属性三2点</t>
+    <t>提升角色的属性三{nature3}点</t>
   </si>
   <si>
     <t>诺亚牌泡腾片</t>
   </si>
   <si>
-    <t>提升属性一12点，减少属性二8点</t>
+    <t>提升角色的属性一{nature1}点，减少角色的属性二{nature2}点</t>
   </si>
   <si>
     <t>金圆券</t>
   </si>
   <si>
-    <t>提升属性一，二1点（在商店卖出的价值较高）</t>
-  </si>
-  <si>
-    <t>提升属性一、二、三各2点</t>
-  </si>
-  <si>
-    <t>提升仙台同学的属性一4，属性二6</t>
-  </si>
-  <si>
-    <t>提升仙台同学属性二20点</t>
-  </si>
-  <si>
-    <t>提升属性一30点，减少属性二10点，属性二减少的数值不会改变</t>
-  </si>
-  <si>
-    <t>提升仙台同学的属性一8，当此牌被剪枝时，不会被消耗</t>
-  </si>
-  <si>
-    <t>提升仙台同学的属性二16，当此牌被生枝时，往手牌中额外加入一张此卡</t>
-  </si>
-  <si>
-    <t>提升属性二14点，被生枝时，提升属性二4点</t>
-  </si>
-  <si>
-    <t>提升属性一12点，被生长时，获得xx金币</t>
-  </si>
-  <si>
-    <t>提升属性一40点，下回合好感度加成减少50%</t>
-  </si>
-  <si>
-    <t>提升属性二10点，被剪枝时，提升属性三10点</t>
-  </si>
-  <si>
-    <t>提升属性一1点，属性二1点，被生长时，额外被生长1次</t>
-  </si>
-  <si>
-    <t>让属性一的数值等于属性二</t>
+    <t>提升角色的属性一{nature1}点，角色的属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>提升角色的属性一、二、三各{nature1}点</t>
+  </si>
+  <si>
+    <t>提升仙台同学的属性一{nature1}点，属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>提升角色的属性一{nature1}点，减少角色的属性二10点，属性二减少的数值不会改变</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(-10,2)</t>
+  </si>
+  <si>
+    <t>提升仙台同学的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
+  </si>
+  <si>
+    <t>noConsumed()</t>
+  </si>
+  <si>
+    <t>提升仙台同学的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
+  </si>
+  <si>
+    <t>addCard(12006,1)</t>
+  </si>
+  <si>
+    <t>提升角色的属性二{nature2}点，被生枝时，提升卡牌的属性二4点</t>
+  </si>
+  <si>
+    <t>addNature(4,2)</t>
+  </si>
+  <si>
+    <t>提升角色的属性一{nature1}点，被生长时，获得40金币</t>
+  </si>
+  <si>
+    <t>addMoney(40)</t>
+  </si>
+  <si>
+    <t>提升角色的属性一{nature1}点，下回合好感度加成减少50%</t>
+  </si>
+  <si>
+    <t>changeProperty(0.5)</t>
+  </si>
+  <si>
+    <t>提升角色的属性二{nature2}点，被剪枝时，提升角色的属性三10点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(10,3)</t>
+  </si>
+  <si>
+    <t>提升角色的属性一{nature1}点，属性二{nature2}点，被生长时，额外触发生长6 1次</t>
+  </si>
+  <si>
+    <t>beAdded(6,1)</t>
+  </si>
+  <si>
+    <t>让角色的属性一的数值等于角色的属性二</t>
+  </si>
+  <si>
+    <t>addNatureFromTo(1,2)</t>
   </si>
 </sst>
 </file>
@@ -140,14 +167,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,137 +640,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -766,8 +786,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1084,12 +1107,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="16.4545454545455" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.8181818181818" customWidth="1"/>
     <col min="6" max="6" width="59.4545454545455" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.2727272727273" customWidth="1"/>
     <col min="8" max="8" width="13.6363636363636" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="18.0909090909091" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.8181818181818" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.2727272727273" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1120,16 +1147,18 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3"/>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -1152,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2">
         <v>10</v>
@@ -1172,7 +1201,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3">
         <v>10</v>
@@ -1192,18 +1221,18 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:20">
+    <row r="5" ht="42" spans="1:20">
       <c r="A5">
         <v>11004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1214,19 +1243,19 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>16</v>
+      <c r="F5" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" ht="28" spans="1:20">
       <c r="A6">
         <v>11005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -1237,8 +1266,8 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>18</v>
+      <c r="F6" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -1249,7 +1278,7 @@
         <v>11006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1260,8 +1289,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
+      <c r="F7" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="I7">
         <v>40</v>
@@ -1280,8 +1309,8 @@
       <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>21</v>
+      <c r="F8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="I8">
         <v>20</v>
@@ -1300,8 +1329,8 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>22</v>
+      <c r="F9" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="I9">
         <v>20</v>
@@ -1320,14 +1349,14 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>23</v>
+      <c r="F10" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="I10">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" ht="28" spans="1:20">
       <c r="A11">
         <v>12004</v>
       </c>
@@ -1335,19 +1364,22 @@
         <v>30</v>
       </c>
       <c r="D11">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
       </c>
       <c r="I11">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" ht="28" spans="1:20">
       <c r="A12">
         <v>12005</v>
       </c>
@@ -1360,11 +1392,14 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>25</v>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="I12">
         <v>20</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:20">
@@ -1380,14 +1415,17 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>26</v>
+      <c r="F13" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="I13">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="J13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:20">
       <c r="A14">
         <v>12007</v>
       </c>
@@ -1400,11 +1438,14 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>27</v>
+      <c r="F14" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="I14">
         <v>20</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1420,14 +1461,17 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>28</v>
+      <c r="F15" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="I15">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="L15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="1:20">
       <c r="A16">
         <v>12009</v>
       </c>
@@ -1440,14 +1484,17 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>29</v>
+      <c r="F16" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="I16">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="M16" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" ht="28" spans="1:12">
       <c r="A17">
         <v>12010</v>
       </c>
@@ -1460,14 +1507,17 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>30</v>
+      <c r="F17" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="I17">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="K17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" ht="28" spans="1:12">
       <c r="A18">
         <v>12011</v>
       </c>
@@ -1480,14 +1530,17 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>31</v>
+      <c r="F18" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="I18">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="L18" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>13001</v>
       </c>
@@ -1500,8 +1553,11 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>32</v>
+      <c r="F19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G19" t="s">
+        <v>41</v>
       </c>
       <c r="I19">
         <v>100</v>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="11950" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -155,6 +155,21 @@
   </si>
   <si>
     <t>addNatureFromTo(1,2)</t>
+  </si>
+  <si>
+    <t>测试用例</t>
+  </si>
+  <si>
+    <t>addCard(11001,1)</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,1,1)</t>
+  </si>
+  <si>
+    <t>addRandomCardIfNot(1,1,1)</t>
+  </si>
+  <si>
+    <t>addMoney(999)</t>
   </si>
 </sst>
 </file>
@@ -320,12 +335,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -646,7 +667,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -670,16 +691,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -688,90 +709,93 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -790,6 +814,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1103,69 +1136,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="8" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.8181818181818" customWidth="1"/>
-    <col min="6" max="6" width="59.4545454545455" style="2" customWidth="1"/>
+    <col min="6" max="6" width="59.4545454545455" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.2727272727273" customWidth="1"/>
     <col min="8" max="8" width="13.6363636363636" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="18.0909090909091" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.8181818181818" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.2727272727273" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.0909090909091" style="3" customWidth="1"/>
+    <col min="11" max="11" width="14.8181818181818" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.2727272727273" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:20">
       <c r="A2">
@@ -1180,7 +1213,7 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I2">
@@ -1200,7 +1233,7 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="I3">
@@ -1220,7 +1253,7 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
       <c r="I4">
@@ -1231,7 +1264,7 @@
       <c r="A5">
         <v>11004</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5">
@@ -1243,7 +1276,7 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I5">
@@ -1254,7 +1287,7 @@
       <c r="A6">
         <v>11005</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C6">
@@ -1266,7 +1299,7 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I6">
@@ -1277,7 +1310,7 @@
       <c r="A7">
         <v>11006</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C7">
@@ -1289,7 +1322,7 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="I7">
@@ -1309,7 +1342,7 @@
       <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
       <c r="I8">
@@ -1329,7 +1362,7 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>23</v>
       </c>
       <c r="I9">
@@ -1349,7 +1382,7 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>14</v>
       </c>
       <c r="I10">
@@ -1369,7 +1402,7 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G11" t="s">
@@ -1392,13 +1425,13 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>26</v>
       </c>
       <c r="I12">
         <v>20</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1415,13 +1448,13 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>28</v>
       </c>
       <c r="I13">
         <v>20</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="3" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1438,13 +1471,13 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>30</v>
       </c>
       <c r="I14">
         <v>20</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="L14" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1461,13 +1494,13 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I15">
         <v>20</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="L15" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1484,17 +1517,17 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>34</v>
       </c>
       <c r="I16">
         <v>20</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" ht="28" spans="1:12">
+    <row r="17" ht="28" spans="1:13">
       <c r="A17">
         <v>12010</v>
       </c>
@@ -1507,17 +1540,17 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="7" t="s">
         <v>36</v>
       </c>
       <c r="I17">
         <v>20</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" ht="28" spans="1:12">
+    <row r="18" ht="28" spans="1:13">
       <c r="A18">
         <v>12011</v>
       </c>
@@ -1530,37 +1563,224 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="7" t="s">
         <v>38</v>
       </c>
       <c r="I18">
         <v>20</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
-      <c r="A19">
+    <row r="19" s="1" customFormat="1" spans="1:13">
+      <c r="A19" s="1">
         <v>13001</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="B19" s="8"/>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="1">
         <v>100</v>
+      </c>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20">
+        <v>11101</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21">
+        <v>11102</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22">
+        <v>11103</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23">
+        <v>11104</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24">
+        <v>11105</v>
+      </c>
+      <c r="C24">
+        <v>6</v>
+      </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25">
+        <v>11106</v>
+      </c>
+      <c r="C25">
+        <v>7</v>
+      </c>
+      <c r="D25">
+        <v>7</v>
+      </c>
+      <c r="E25">
+        <v>7</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26">
+        <v>11107</v>
+      </c>
+      <c r="C26">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>8</v>
+      </c>
+      <c r="E26">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27">
+        <v>11108</v>
+      </c>
+      <c r="C27">
+        <v>9</v>
+      </c>
+      <c r="D27">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28">
+        <v>11109</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29">
+        <v>11110</v>
+      </c>
+      <c r="C29">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>11</v>
+      </c>
+      <c r="E29">
+        <v>11</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11950" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
   <si>
     <t>id</t>
   </si>
@@ -70,12 +70,24 @@
     <t>nextTurn</t>
   </si>
   <si>
+    <t>Icon</t>
+  </si>
+  <si>
+    <t>八万霜叶</t>
+  </si>
+  <si>
     <t>提升角色的属性一{nature1}点</t>
   </si>
   <si>
+    <t>柳荫不眠</t>
+  </si>
+  <si>
     <t>提升角色的属性二{nature2}点</t>
   </si>
   <si>
+    <t>根状茎</t>
+  </si>
+  <si>
     <t>提升角色的属性一{nature1}点，属性二{nature2}点</t>
   </si>
   <si>
@@ -97,79 +109,100 @@
     <t>提升角色的属性一{nature1}点，角色的属性二{nature2}点</t>
   </si>
   <si>
+    <t>新芽令</t>
+  </si>
+  <si>
     <t>提升角色的属性一、二、三各{nature1}点</t>
   </si>
   <si>
+    <t>叶缘微光</t>
+  </si>
+  <si>
     <t>提升仙台同学的属性一{nature1}点，属性二{nature2}点</t>
   </si>
   <si>
+    <t>不老年轮</t>
+  </si>
+  <si>
+    <t>无心之柳</t>
+  </si>
+  <si>
     <t>提升角色的属性一{nature1}点，减少角色的属性二10点，属性二减少的数值不会改变</t>
   </si>
   <si>
     <t>addNatureAtSum(-10,2)</t>
   </si>
   <si>
+    <t>不眠精灵</t>
+  </si>
+  <si>
     <t>提升仙台同学的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
   </si>
   <si>
     <t>noConsumed()</t>
   </si>
   <si>
+    <t>永生山杨</t>
+  </si>
+  <si>
     <t>提升仙台同学的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
   </si>
   <si>
     <t>addCard(12006,1)</t>
   </si>
   <si>
+    <t>柳成荫</t>
+  </si>
+  <si>
     <t>提升角色的属性二{nature2}点，被生枝时，提升卡牌的属性二4点</t>
   </si>
   <si>
     <t>addNature(4,2)</t>
   </si>
   <si>
+    <t>春湖倒影</t>
+  </si>
+  <si>
     <t>提升角色的属性一{nature1}点，被生长时，获得40金币</t>
   </si>
   <si>
     <t>addMoney(40)</t>
   </si>
   <si>
+    <t>枯荣令</t>
+  </si>
+  <si>
     <t>提升角色的属性一{nature1}点，下回合好感度加成减少50%</t>
   </si>
   <si>
     <t>changeProperty(0.5)</t>
   </si>
   <si>
+    <t>晨露叶</t>
+  </si>
+  <si>
     <t>提升角色的属性二{nature2}点，被剪枝时，提升角色的属性三10点</t>
   </si>
   <si>
     <t>addNatureAtSum(10,3)</t>
   </si>
   <si>
+    <t>正午柳</t>
+  </si>
+  <si>
     <t>提升角色的属性一{nature1}点，属性二{nature2}点，被生长时，额外触发生长6 1次</t>
   </si>
   <si>
     <t>beAdded(6,1)</t>
   </si>
   <si>
+    <t>无心之影</t>
+  </si>
+  <si>
     <t>让角色的属性一的数值等于角色的属性二</t>
   </si>
   <si>
     <t>addNatureFromTo(1,2)</t>
-  </si>
-  <si>
-    <t>测试用例</t>
-  </si>
-  <si>
-    <t>addCard(11001,1)</t>
-  </si>
-  <si>
-    <t>addRandomCard(1,1,1)</t>
-  </si>
-  <si>
-    <t>addRandomCardIfNot(1,1,1)</t>
-  </si>
-  <si>
-    <t>addMoney(999)</t>
   </si>
 </sst>
 </file>
@@ -182,13 +215,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -661,133 +700,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -810,14 +849,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1136,11 +1175,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T29"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="8" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11.8181818181818" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.8181818181818" customWidth="1"/>
     <col min="6" max="6" width="59.4545454545455" style="3" customWidth="1"/>
     <col min="7" max="7" width="19.2727272727273" customWidth="1"/>
@@ -1192,7 +1231,9 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4"/>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
@@ -1204,6 +1245,9 @@
       <c r="A2">
         <v>11001</v>
       </c>
+      <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
       <c r="C2">
         <v>8</v>
       </c>
@@ -1213,17 +1257,20 @@
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>13</v>
+      <c r="F2" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="I2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" ht="17.5" spans="1:20">
       <c r="A3">
         <v>11002</v>
       </c>
+      <c r="B3" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="C3">
         <v>0</v>
       </c>
@@ -1233,17 +1280,20 @@
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>14</v>
+      <c r="F3" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="I3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" ht="17.5" spans="1:20">
       <c r="A4">
         <v>11003</v>
       </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="C4">
         <v>2</v>
       </c>
@@ -1253,19 +1303,19 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>15</v>
+      <c r="F4" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="42" spans="1:20">
+    <row r="5" ht="28" spans="1:20">
       <c r="A5">
         <v>11004</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1276,8 +1326,8 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>17</v>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -1288,7 +1338,7 @@
         <v>11005</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -1299,8 +1349,8 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>19</v>
+      <c r="F6" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -1311,7 +1361,7 @@
         <v>11006</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1322,17 +1372,20 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>21</v>
+      <c r="F7" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="I7">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" ht="17.5" spans="1:20">
       <c r="A8">
         <v>12001</v>
       </c>
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="C8">
         <v>2</v>
       </c>
@@ -1342,17 +1395,20 @@
       <c r="E8">
         <v>2</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>22</v>
+      <c r="F8" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="I8">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" ht="17.5" spans="1:20">
       <c r="A9">
         <v>12002</v>
       </c>
+      <c r="B9" s="6" t="s">
+        <v>28</v>
+      </c>
       <c r="C9">
         <v>4</v>
       </c>
@@ -1362,17 +1418,20 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>23</v>
+      <c r="F9" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="I9">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" ht="17.5" spans="1:20">
       <c r="A10">
         <v>12003</v>
       </c>
+      <c r="B10" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="C10">
         <v>0</v>
       </c>
@@ -1382,8 +1441,8 @@
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
+      <c r="F10" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="I10">
         <v>20</v>
@@ -1393,6 +1452,9 @@
       <c r="A11">
         <v>12004</v>
       </c>
+      <c r="B11" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="C11">
         <v>30</v>
       </c>
@@ -1402,11 +1464,11 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>24</v>
+      <c r="F11" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>20</v>
@@ -1416,6 +1478,9 @@
       <c r="A12">
         <v>12005</v>
       </c>
+      <c r="B12" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="C12">
         <v>8</v>
       </c>
@@ -1425,20 +1490,23 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>26</v>
+      <c r="F12" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="I12">
         <v>20</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:20">
       <c r="A13">
         <v>12006</v>
       </c>
+      <c r="B13" s="6" t="s">
+        <v>37</v>
+      </c>
       <c r="C13">
         <v>0</v>
       </c>
@@ -1448,20 +1516,23 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>28</v>
+      <c r="F13" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="I13">
         <v>20</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:20">
       <c r="A14">
         <v>12007</v>
       </c>
+      <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="C14">
         <v>0</v>
       </c>
@@ -1471,20 +1542,23 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>30</v>
+      <c r="F14" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="I14">
         <v>20</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" ht="17.5" spans="1:20">
       <c r="A15">
         <v>12008</v>
       </c>
+      <c r="B15" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="C15">
         <v>12</v>
       </c>
@@ -1494,20 +1568,23 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>32</v>
+      <c r="F15" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="I15">
         <v>20</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="28" spans="1:20">
       <c r="A16">
         <v>12009</v>
       </c>
+      <c r="B16" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="C16">
         <v>40</v>
       </c>
@@ -1517,20 +1594,23 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>34</v>
+      <c r="F16" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="I16">
         <v>20</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" ht="28" spans="1:13">
       <c r="A17">
         <v>12010</v>
       </c>
+      <c r="B17" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="C17">
         <v>0</v>
       </c>
@@ -1540,20 +1620,23 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>36</v>
+      <c r="F17" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="I17">
         <v>20</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" ht="28" spans="1:13">
       <c r="A18">
         <v>12011</v>
       </c>
+      <c r="B18" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="C18">
         <v>2</v>
       </c>
@@ -1563,21 +1646,23 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>38</v>
+      <c r="F18" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="I18">
         <v>20</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:13">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="17.5" spans="1:13">
       <c r="A19" s="1">
         <v>13001</v>
       </c>
-      <c r="B19" s="8"/>
+      <c r="B19" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="C19" s="1">
         <v>0</v>
       </c>
@@ -1588,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I19" s="1">
         <v>100</v>
@@ -1600,188 +1685,6 @@
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20">
-        <v>11101</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21">
-        <v>11102</v>
-      </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22">
-        <v>11103</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22">
-        <v>4</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23">
-        <v>11104</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24">
-        <v>11105</v>
-      </c>
-      <c r="C24">
-        <v>6</v>
-      </c>
-      <c r="D24">
-        <v>6</v>
-      </c>
-      <c r="E24">
-        <v>6</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25">
-        <v>11106</v>
-      </c>
-      <c r="C25">
-        <v>7</v>
-      </c>
-      <c r="D25">
-        <v>7</v>
-      </c>
-      <c r="E25">
-        <v>7</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26">
-        <v>11107</v>
-      </c>
-      <c r="C26">
-        <v>8</v>
-      </c>
-      <c r="D26">
-        <v>8</v>
-      </c>
-      <c r="E26">
-        <v>8</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27">
-        <v>11108</v>
-      </c>
-      <c r="C27">
-        <v>9</v>
-      </c>
-      <c r="D27">
-        <v>9</v>
-      </c>
-      <c r="E27">
-        <v>9</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28">
-        <v>11109</v>
-      </c>
-      <c r="C28">
-        <v>10</v>
-      </c>
-      <c r="D28">
-        <v>10</v>
-      </c>
-      <c r="E28">
-        <v>10</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29">
-        <v>11110</v>
-      </c>
-      <c r="C29">
-        <v>11</v>
-      </c>
-      <c r="D29">
-        <v>11</v>
-      </c>
-      <c r="E29">
-        <v>11</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>42</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
   <si>
     <t>id</t>
   </si>
@@ -73,18 +73,24 @@
     <t>Icon</t>
   </si>
   <si>
+    <t>初始礼物1</t>
+  </si>
+  <si>
+    <t>提升角色的属性一{nature1}点</t>
+  </si>
+  <si>
+    <t>初始礼物2</t>
+  </si>
+  <si>
+    <t>提升角色的属性二{nature2}点</t>
+  </si>
+  <si>
     <t>八万霜叶</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点</t>
-  </si>
-  <si>
     <t>柳荫不眠</t>
   </si>
   <si>
-    <t>提升角色的属性二{nature2}点</t>
-  </si>
-  <si>
     <t>根状茎</t>
   </si>
   <si>
@@ -203,6 +209,147 @@
   </si>
   <si>
     <t>addNatureFromTo(1,2)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌01</t>
+  </si>
+  <si>
+    <t>测试使用</t>
+  </si>
+  <si>
+    <t>addNature(4,1)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌02</t>
+  </si>
+  <si>
+    <t>addnaturefromTo</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌03</t>
+  </si>
+  <si>
+    <t>addcard</t>
+  </si>
+  <si>
+    <t>addCard(11001,1)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌04</t>
+  </si>
+  <si>
+    <t>addran</t>
+  </si>
+  <si>
+    <t>addRandomCard(2,1,2)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌05</t>
+  </si>
+  <si>
+    <t>addmoney</t>
+  </si>
+  <si>
+    <t>addMoney(1001)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌06</t>
+  </si>
+  <si>
+    <t>changepro</t>
+  </si>
+  <si>
+    <t>changeProperty(2)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌07</t>
+  </si>
+  <si>
+    <t>beadd</t>
+  </si>
+  <si>
+    <t>beAdded(1,8)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌08</t>
+  </si>
+  <si>
+    <t>beaddto</t>
+  </si>
+  <si>
+    <t>beAddedTo(20)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌09</t>
+  </si>
+  <si>
+    <t>触发生枝（手工）times次</t>
+  </si>
+  <si>
+    <t>beMade(1)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌10</t>
+  </si>
+  <si>
+    <t>触发剪枝（拆卸）times次</t>
+  </si>
+  <si>
+    <t>beBroken(1)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌11</t>
+  </si>
+  <si>
+    <t>功能卡增加add的数值num点</t>
+  </si>
+  <si>
+    <t>addAddNum</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌12</t>
+  </si>
+  <si>
+    <t>若卡组中有sameNum个及以上相同的礼物，生长trueNum，否则生长falseNum</t>
+  </si>
+  <si>
+    <t>addWithSame(3,40,5)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌13</t>
+  </si>
+  <si>
+    <t>若卡组中有sameNum个及以上相同的礼物，生长所有这些相同的礼物addNum</t>
+  </si>
+  <si>
+    <t>addWIthSameTogether(3,100)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌14</t>
+  </si>
+  <si>
+    <t>将手牌中所有礼物变成一个随机礼物</t>
+  </si>
+  <si>
+    <t>changeHandGift()</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌15</t>
+  </si>
+  <si>
+    <t>若卡牌的type1属性大于0（存在），提升角色的type属性40</t>
+  </si>
+  <si>
+    <t>addNatureAtSumIf(1,50)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌16</t>
+  </si>
+  <si>
+    <t>获得n2属性(n1)/2点</t>
+  </si>
+  <si>
+    <t>addNatureByOther(1,2)</t>
   </si>
 </sst>
 </file>
@@ -215,7 +362,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +375,13 @@
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -374,7 +528,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,6 +538,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2972F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -700,55 +860,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
@@ -763,74 +920,77 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -863,6 +1023,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1175,7 +1341,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
@@ -1241,450 +1407,889 @@
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:20">
-      <c r="A2">
+    <row r="2" spans="1:20">
+      <c r="A2" s="4">
+        <v>11601</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="4">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="4">
+        <v>11602</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:20">
+      <c r="A4">
         <v>11001</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>8</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" ht="17.5" spans="1:20">
-      <c r="A3">
-        <v>11002</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>12</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" ht="17.5" spans="1:20">
-      <c r="A4">
-        <v>11003</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I4">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:20">
+    <row r="5" ht="17.5" spans="1:20">
       <c r="A5">
-        <v>11004</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>11002</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="I5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:20">
+    <row r="6" ht="17.5" spans="1:20">
       <c r="A6">
-        <v>11005</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>11003</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>23</v>
+      <c r="F6" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="I6">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" ht="28" spans="1:20">
       <c r="A7">
+        <v>11004</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:20">
+      <c r="A8">
+        <v>11005</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>-8</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9">
         <v>11006</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9">
         <v>40</v>
-      </c>
-    </row>
-    <row r="8" ht="17.5" spans="1:20">
-      <c r="A8">
-        <v>12001</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="I8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="17.5" spans="1:20">
-      <c r="A9">
-        <v>12002</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9">
-        <v>20</v>
       </c>
     </row>
     <row r="10" ht="17.5" spans="1:20">
       <c r="A10">
-        <v>12003</v>
+        <v>12001</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="I10">
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="28" spans="1:20">
+    <row r="11" ht="17.5" spans="1:20">
       <c r="A11">
-        <v>12004</v>
+        <v>12002</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="C11">
-        <v>30</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" t="s">
-        <v>33</v>
       </c>
       <c r="I11">
         <v>20</v>
       </c>
     </row>
-    <row r="12" ht="28" spans="1:20">
+    <row r="12" ht="17.5" spans="1:20">
       <c r="A12">
-        <v>12005</v>
+        <v>12003</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="I12">
         <v>20</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1" spans="1:20">
+    </row>
+    <row r="13" ht="28" spans="1:20">
       <c r="A13">
-        <v>12006</v>
+        <v>12004</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
       </c>
       <c r="I13">
         <v>20</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:20">
+    </row>
+    <row r="14" ht="28" spans="1:20">
       <c r="A14">
-        <v>12007</v>
+        <v>12005</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="I14">
         <v>20</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" ht="17.5" spans="1:20">
+      <c r="K14" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1" spans="1:20">
       <c r="A15">
-        <v>12008</v>
+        <v>12006</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I15">
         <v>20</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" ht="28" spans="1:20">
+      <c r="J15" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:20">
       <c r="A16">
-        <v>12009</v>
+        <v>12007</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C16">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I16">
         <v>20</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" ht="28" spans="1:13">
+      <c r="L16" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" ht="17.5" spans="1:13">
       <c r="A17">
-        <v>12010</v>
+        <v>12008</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I17">
         <v>20</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>51</v>
+      <c r="L17" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="28" spans="1:13">
       <c r="A18">
-        <v>12011</v>
+        <v>12009</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I18">
         <v>20</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="M18" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:13">
+      <c r="A19">
+        <v>12010</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>10</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19">
+        <v>20</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:13">
+      <c r="A20">
+        <v>12011</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="17.5" spans="1:13">
-      <c r="A19" s="1">
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20">
+        <v>20</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="17.5" spans="1:13">
+      <c r="A21" s="1">
         <v>13001</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="1">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="B21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="1">
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I21" s="1">
         <v>100</v>
       </c>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" ht="28" spans="1:13">
+      <c r="A22">
+        <v>11201</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" ht="28" spans="1:13">
+      <c r="A23">
+        <v>11202</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" ht="28" spans="1:13">
+      <c r="A24">
+        <v>11203</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" ht="28" spans="1:13">
+      <c r="A25">
+        <v>11204</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" ht="28" spans="1:13">
+      <c r="A26">
+        <v>11205</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" ht="28" spans="1:13">
+      <c r="A27">
+        <v>11206</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27">
+        <v>6</v>
+      </c>
+      <c r="D27">
+        <v>6</v>
+      </c>
+      <c r="E27">
+        <v>6</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" ht="28" spans="1:13">
+      <c r="A28">
+        <v>11207</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28">
+        <v>7</v>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28">
+        <v>7</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" ht="28" spans="1:13">
+      <c r="A29">
+        <v>11208</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29">
+        <v>8</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" ht="28" spans="1:13">
+      <c r="A30">
+        <v>11209</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>9</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" ht="28" spans="1:13">
+      <c r="A31">
+        <v>11210</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" ht="28" spans="1:13">
+      <c r="A32">
+        <v>11211</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>11</v>
+      </c>
+      <c r="E32">
+        <v>11</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" ht="28" spans="1:7">
+      <c r="A33">
+        <v>11212</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33">
+        <v>12</v>
+      </c>
+      <c r="D33">
+        <v>12</v>
+      </c>
+      <c r="E33">
+        <v>12</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" ht="28" spans="1:7">
+      <c r="A34">
+        <v>11213</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34">
+        <v>13</v>
+      </c>
+      <c r="D34">
+        <v>13</v>
+      </c>
+      <c r="E34">
+        <v>13</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" ht="28" spans="1:7">
+      <c r="A35">
+        <v>11214</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35">
+        <v>14</v>
+      </c>
+      <c r="D35">
+        <v>14</v>
+      </c>
+      <c r="E35">
+        <v>14</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" ht="28" spans="1:7">
+      <c r="A36">
+        <v>11215</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C36">
+        <v>15</v>
+      </c>
+      <c r="D36">
+        <v>15</v>
+      </c>
+      <c r="E36">
+        <v>15</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" ht="28" spans="1:7">
+      <c r="A37">
+        <v>11216</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>16</v>
+      </c>
+      <c r="D37">
+        <v>16</v>
+      </c>
+      <c r="E37">
+        <v>16</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="F38" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="81">
   <si>
     <t>id</t>
   </si>
@@ -214,25 +214,19 @@
     <t>测试礼物卡牌01</t>
   </si>
   <si>
-    <t>测试使用</t>
-  </si>
-  <si>
     <t>addNature(4,1)</t>
   </si>
   <si>
     <t>测试礼物卡牌02</t>
   </si>
   <si>
-    <t>addnaturefromTo</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌03</t>
-  </si>
-  <si>
-    <t>addcard</t>
-  </si>
-  <si>
-    <t>addCard(11001,1)</t>
+    <t>addNatureTo(1001,2)</t>
+  </si>
+  <si>
+    <t>测试礼物卡牌03！</t>
+  </si>
+  <si>
+    <t>addNatureAtSumIf(1,2)</t>
   </si>
   <si>
     <t>测试礼物卡牌04</t>
@@ -278,78 +272,6 @@
   </si>
   <si>
     <t>beAddedTo(20)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌09</t>
-  </si>
-  <si>
-    <t>触发生枝（手工）times次</t>
-  </si>
-  <si>
-    <t>beMade(1)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌10</t>
-  </si>
-  <si>
-    <t>触发剪枝（拆卸）times次</t>
-  </si>
-  <si>
-    <t>beBroken(1)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌11</t>
-  </si>
-  <si>
-    <t>功能卡增加add的数值num点</t>
-  </si>
-  <si>
-    <t>addAddNum</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌12</t>
-  </si>
-  <si>
-    <t>若卡组中有sameNum个及以上相同的礼物，生长trueNum，否则生长falseNum</t>
-  </si>
-  <si>
-    <t>addWithSame(3,40,5)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌13</t>
-  </si>
-  <si>
-    <t>若卡组中有sameNum个及以上相同的礼物，生长所有这些相同的礼物addNum</t>
-  </si>
-  <si>
-    <t>addWIthSameTogether(3,100)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌14</t>
-  </si>
-  <si>
-    <t>将手牌中所有礼物变成一个随机礼物</t>
-  </si>
-  <si>
-    <t>changeHandGift()</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌15</t>
-  </si>
-  <si>
-    <t>若卡牌的type1属性大于0（存在），提升角色的type属性40</t>
-  </si>
-  <si>
-    <t>addNatureAtSumIf(1,50)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌16</t>
-  </si>
-  <si>
-    <t>获得n2属性(n1)/2点</t>
-  </si>
-  <si>
-    <t>addNatureByOther(1,2)</t>
   </si>
 </sst>
 </file>
@@ -528,7 +450,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,12 +460,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2972F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -866,7 +782,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -890,16 +806,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
@@ -908,89 +824,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1023,9 +939,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1341,7 +1254,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T38"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
@@ -1937,10 +1850,10 @@
         <v>1</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" t="s">
         <v>61</v>
-      </c>
-      <c r="G22" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:13">
@@ -1948,7 +1861,7 @@
         <v>11202</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -1960,10 +1873,10 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" ht="28" spans="1:13">
@@ -1971,7 +1884,7 @@
         <v>11203</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -1983,10 +1896,10 @@
         <v>3</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:13">
@@ -1994,7 +1907,7 @@
         <v>11204</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -2006,10 +1919,10 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" ht="28" spans="1:13">
@@ -2017,7 +1930,7 @@
         <v>11205</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -2029,10 +1942,10 @@
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" ht="28" spans="1:13">
@@ -2040,7 +1953,7 @@
         <v>11206</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -2052,10 +1965,10 @@
         <v>6</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:13">
@@ -2063,7 +1976,7 @@
         <v>11207</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -2075,10 +1988,10 @@
         <v>7</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" ht="28" spans="1:13">
@@ -2086,7 +1999,7 @@
         <v>11208</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -2098,198 +2011,14 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" ht="28" spans="1:13">
-      <c r="A30">
-        <v>11209</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30">
-        <v>9</v>
-      </c>
-      <c r="D30">
-        <v>9</v>
-      </c>
-      <c r="E30">
-        <v>9</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" ht="28" spans="1:13">
-      <c r="A31">
-        <v>11210</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31">
-        <v>10</v>
-      </c>
-      <c r="D31">
-        <v>10</v>
-      </c>
-      <c r="E31">
-        <v>10</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" ht="28" spans="1:13">
-      <c r="A32">
-        <v>11211</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32">
-        <v>11</v>
-      </c>
-      <c r="D32">
-        <v>11</v>
-      </c>
-      <c r="E32">
-        <v>11</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" ht="28" spans="1:7">
-      <c r="A33">
-        <v>11212</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33">
-        <v>12</v>
-      </c>
-      <c r="D33">
-        <v>12</v>
-      </c>
-      <c r="E33">
-        <v>12</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" ht="28" spans="1:7">
-      <c r="A34">
-        <v>11213</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34">
-        <v>13</v>
-      </c>
-      <c r="D34">
-        <v>13</v>
-      </c>
-      <c r="E34">
-        <v>13</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" ht="28" spans="1:7">
-      <c r="A35">
-        <v>11214</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35">
-        <v>14</v>
-      </c>
-      <c r="D35">
-        <v>14</v>
-      </c>
-      <c r="E35">
-        <v>14</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" ht="28" spans="1:7">
-      <c r="A36">
-        <v>11215</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36">
-        <v>15</v>
-      </c>
-      <c r="D36">
-        <v>15</v>
-      </c>
-      <c r="E36">
-        <v>15</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" ht="28" spans="1:7">
-      <c r="A37">
-        <v>11216</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37">
-        <v>16</v>
-      </c>
-      <c r="D37">
-        <v>16</v>
-      </c>
-      <c r="E37">
-        <v>16</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="F38" s="12"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="F30" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
   <si>
     <t>id</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Icon</t>
+  </si>
+  <si>
+    <t>dialog</t>
   </si>
   <si>
     <t>初始礼物1</t>
@@ -1313,7 +1316,9 @@
       <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4"/>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
@@ -1325,7 +1330,7 @@
         <v>11601</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4">
         <v>4</v>
@@ -1337,7 +1342,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -1347,7 +1352,9 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
@@ -1359,7 +1366,7 @@
         <v>11602</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
@@ -1371,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -1381,7 +1388,9 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -1393,7 +1402,7 @@
         <v>11001</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1405,10 +1414,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4">
         <v>10</v>
+      </c>
+      <c r="O4">
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="17.5" spans="1:20">
@@ -1416,7 +1428,7 @@
         <v>11002</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1428,10 +1440,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5">
         <v>10</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="17.5" spans="1:20">
@@ -1439,7 +1454,7 @@
         <v>11003</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1451,10 +1466,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6">
         <v>10</v>
+      </c>
+      <c r="O6" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:20">
@@ -1462,7 +1480,7 @@
         <v>11004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1474,10 +1492,13 @@
         <v>2</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I7">
         <v>10</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:20">
@@ -1485,7 +1506,7 @@
         <v>11005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -1497,10 +1518,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8">
         <v>10</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1508,7 +1532,7 @@
         <v>11006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1520,10 +1544,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I9">
         <v>40</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="17.5" spans="1:20">
@@ -1531,7 +1558,7 @@
         <v>12001</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1543,10 +1570,13 @@
         <v>2</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I10">
         <v>20</v>
+      </c>
+      <c r="O10">
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="17.5" spans="1:20">
@@ -1554,7 +1584,7 @@
         <v>12002</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -1566,10 +1596,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I11">
         <v>20</v>
+      </c>
+      <c r="O11" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="17.5" spans="1:20">
@@ -1577,7 +1610,7 @@
         <v>12003</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1589,10 +1622,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12">
         <v>20</v>
+      </c>
+      <c r="O12" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="28" spans="1:20">
@@ -1600,7 +1636,7 @@
         <v>12004</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>30</v>
@@ -1612,13 +1648,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I13">
         <v>20</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="28" spans="1:20">
@@ -1626,7 +1665,7 @@
         <v>12005</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1638,13 +1677,16 @@
         <v>0</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I14">
         <v>20</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="O14" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:20">
@@ -1652,7 +1694,7 @@
         <v>12006</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1664,13 +1706,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I15">
         <v>20</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="O15" s="4">
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:20">
@@ -1678,7 +1723,7 @@
         <v>12007</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1690,21 +1735,24 @@
         <v>0</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I16">
         <v>20</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" ht="17.5" spans="1:13">
+        <v>45</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="17.5" spans="1:15">
       <c r="A17">
         <v>12008</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -1716,21 +1764,24 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I17">
         <v>20</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" ht="28" spans="1:13">
+        <v>48</v>
+      </c>
+      <c r="O17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="28" spans="1:15">
       <c r="A18">
         <v>12009</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -1742,21 +1793,24 @@
         <v>0</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I18">
         <v>20</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" ht="28" spans="1:13">
+        <v>51</v>
+      </c>
+      <c r="O18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:15">
       <c r="A19">
         <v>12010</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1768,21 +1822,24 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I19">
         <v>20</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" ht="28" spans="1:13">
+        <v>54</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:15">
       <c r="A20">
         <v>12011</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -1794,21 +1851,24 @@
         <v>0</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I20">
         <v>20</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="17.5" spans="1:13">
+        <v>57</v>
+      </c>
+      <c r="O20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="17.5" spans="1:15">
       <c r="A21" s="1">
         <v>13001</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -1820,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I21" s="1">
         <v>100</v>
@@ -1832,13 +1892,16 @@
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
-    </row>
-    <row r="22" ht="28" spans="1:13">
+      <c r="O21" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:15">
       <c r="A22">
         <v>11201</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1850,18 +1913,18 @@
         <v>1</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" ht="28" spans="1:13">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" ht="28" spans="1:15">
       <c r="A23">
         <v>11202</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -1873,18 +1936,18 @@
         <v>2</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" ht="28" spans="1:13">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" ht="28" spans="1:15">
       <c r="A24">
         <v>11203</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -1896,18 +1959,18 @@
         <v>3</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" ht="28" spans="1:13">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" ht="28" spans="1:15">
       <c r="A25">
         <v>11204</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -1919,18 +1982,18 @@
         <v>4</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G25" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" ht="28" spans="1:13">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" ht="28" spans="1:15">
       <c r="A26">
         <v>11205</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -1942,18 +2005,18 @@
         <v>5</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" ht="28" spans="1:13">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" ht="28" spans="1:15">
       <c r="A27">
         <v>11206</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -1965,18 +2028,18 @@
         <v>6</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" ht="28" spans="1:13">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" ht="28" spans="1:15">
       <c r="A28">
         <v>11207</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28">
         <v>7</v>
@@ -1988,18 +2051,18 @@
         <v>7</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" ht="28" spans="1:13">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" ht="28" spans="1:15">
       <c r="A29">
         <v>11208</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -2011,13 +2074,13 @@
         <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="F30" s="11"/>
     </row>
   </sheetData>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -275,6 +275,15 @@
   </si>
   <si>
     <t>beAddedTo(20)</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>000</t>
+  </si>
+  <si>
+    <t>addNatureByOther(1,2)</t>
   </si>
 </sst>
 </file>
@@ -944,6 +953,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2081,7 +2093,18 @@
       </c>
     </row>
     <row r="30" spans="1:15">
-      <c r="F30" s="11"/>
+      <c r="A30">
+        <v>18888</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" t="s">
+        <v>84</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -1353,7 +1353,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -1389,7 +1389,7 @@
       <c r="M3" s="2"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="5" ht="17.5" spans="1:20">
       <c r="A5">
-        <v>11002</v>
+        <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>20</v>
@@ -1446,7 +1446,7 @@
         <v>10</v>
       </c>
       <c r="O5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" ht="17.5" spans="1:20">
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="O6" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" ht="28" spans="1:20">
@@ -1498,7 +1498,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="28" spans="1:20">
@@ -1524,7 +1524,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1550,7 +1550,7 @@
         <v>40</v>
       </c>
       <c r="O9" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="17.5" spans="1:20">
@@ -1602,7 +1602,7 @@
         <v>20</v>
       </c>
       <c r="O11" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" ht="17.5" spans="1:20">
@@ -1628,7 +1628,7 @@
         <v>20</v>
       </c>
       <c r="O12" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" ht="28" spans="1:20">
@@ -1657,7 +1657,7 @@
         <v>20</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" ht="28" spans="1:20">
@@ -1686,7 +1686,7 @@
         <v>39</v>
       </c>
       <c r="O14" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:20">
@@ -1715,7 +1715,7 @@
         <v>42</v>
       </c>
       <c r="O15" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:20">
@@ -1744,7 +1744,7 @@
         <v>45</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" ht="17.5" spans="1:15">
@@ -1773,7 +1773,7 @@
         <v>48</v>
       </c>
       <c r="O17" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" ht="28" spans="1:15">
@@ -1802,7 +1802,7 @@
         <v>51</v>
       </c>
       <c r="O18" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="28" spans="1:15">
@@ -1831,7 +1831,7 @@
         <v>54</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="28" spans="1:15">
@@ -1860,7 +1860,7 @@
         <v>57</v>
       </c>
       <c r="O20" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="17.5" spans="1:15">
@@ -1893,7 +1893,7 @@
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
       <c r="O21" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:15">

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>id</t>
   </si>
@@ -212,69 +212,6 @@
   </si>
   <si>
     <t>addNatureFromTo(1,2)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌01</t>
-  </si>
-  <si>
-    <t>addNature(4,1)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌02</t>
-  </si>
-  <si>
-    <t>addNatureTo(1001,2)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌03！</t>
-  </si>
-  <si>
-    <t>addNatureAtSumIf(1,2)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌04</t>
-  </si>
-  <si>
-    <t>addran</t>
-  </si>
-  <si>
-    <t>addRandomCard(2,1,2)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌05</t>
-  </si>
-  <si>
-    <t>addmoney</t>
-  </si>
-  <si>
-    <t>addMoney(1001)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌06</t>
-  </si>
-  <si>
-    <t>changepro</t>
-  </si>
-  <si>
-    <t>changeProperty(2)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌07</t>
-  </si>
-  <si>
-    <t>beadd</t>
-  </si>
-  <si>
-    <t>beAdded(1,8)</t>
-  </si>
-  <si>
-    <t>测试礼物卡牌08</t>
-  </si>
-  <si>
-    <t>beaddto</t>
-  </si>
-  <si>
-    <t>beAddedTo(20)</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1194,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
@@ -1896,192 +1833,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" ht="28" spans="1:15">
-      <c r="A22">
-        <v>11201</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" ht="28" spans="1:15">
-      <c r="A23">
-        <v>11202</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" ht="28" spans="1:15">
-      <c r="A24">
-        <v>11203</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" ht="28" spans="1:15">
-      <c r="A25">
-        <v>11204</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25">
-        <v>4</v>
-      </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" ht="28" spans="1:15">
-      <c r="A26">
-        <v>11205</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26">
-        <v>5</v>
-      </c>
-      <c r="D26">
-        <v>5</v>
-      </c>
-      <c r="E26">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" ht="28" spans="1:15">
-      <c r="A27">
-        <v>11206</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27">
-        <v>6</v>
-      </c>
-      <c r="D27">
-        <v>6</v>
-      </c>
-      <c r="E27">
-        <v>6</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G27" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" ht="28" spans="1:15">
-      <c r="A28">
-        <v>11207</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28">
-        <v>7</v>
-      </c>
-      <c r="D28">
-        <v>7</v>
-      </c>
-      <c r="E28">
-        <v>7</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" ht="28" spans="1:15">
-      <c r="A29">
-        <v>11208</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29">
-        <v>8</v>
-      </c>
-      <c r="D29">
-        <v>8</v>
-      </c>
-      <c r="E29">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="G29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
-      <c r="F30" s="11"/>
+    <row r="22" spans="1:15">
+      <c r="F22" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
   <si>
     <t>id</t>
   </si>
@@ -79,13 +79,13 @@
     <t>初始礼物1</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点</t>
+    <t>提升蒂娜的属性一{nature1}点</t>
   </si>
   <si>
     <t>初始礼物2</t>
   </si>
   <si>
-    <t>提升角色的属性二{nature2}点</t>
+    <t>提升蒂娜的属性二{nature2}点</t>
   </si>
   <si>
     <t>八万霜叶</t>
@@ -97,46 +97,43 @@
     <t>根状茎</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点，属性二{nature2}点</t>
+    <t>提升蒂娜的属性一{nature1}点，属性二{nature2}点</t>
   </si>
   <si>
     <t>雪莉牌手榨苹果汁</t>
   </si>
   <si>
-    <t>提升角色的属性三{nature3}点</t>
+    <t>提升蒂娜的属性三{nature3}点</t>
   </si>
   <si>
     <t>诺亚牌泡腾片</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点，减少角色的属性二{nature2}点</t>
+    <t>提升蒂娜的属性一{nature1}点，减少蒂娜的属性二{nature2}点</t>
   </si>
   <si>
     <t>金圆券</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点，角色的属性二{nature2}点</t>
+    <t>提升蒂娜的属性一{nature1}点，蒂娜的属性二{nature2}点</t>
   </si>
   <si>
     <t>新芽令</t>
   </si>
   <si>
-    <t>提升角色的属性一、二、三各{nature1}点</t>
+    <t>提升蒂娜的属性一、二、三各{nature1}点</t>
   </si>
   <si>
     <t>叶缘微光</t>
   </si>
   <si>
-    <t>提升仙台同学的属性一{nature1}点，属性二{nature2}点</t>
-  </si>
-  <si>
     <t>不老年轮</t>
   </si>
   <si>
     <t>无心之柳</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点，减少角色的属性二10点，属性二减少的数值不会改变</t>
+    <t>提升蒂娜的属性一{nature1}点，减少蒂娜的属性二10点，属性二减少的数值不会改变</t>
   </si>
   <si>
     <t>addNatureAtSum(-10,2)</t>
@@ -145,7 +142,7 @@
     <t>不眠精灵</t>
   </si>
   <si>
-    <t>提升仙台同学的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
+    <t>提升蒂娜的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
   </si>
   <si>
     <t>noConsumed()</t>
@@ -154,7 +151,7 @@
     <t>永生山杨</t>
   </si>
   <si>
-    <t>提升仙台同学的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
+    <t>提升蒂娜的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
   </si>
   <si>
     <t>addCard(12006,1)</t>
@@ -163,7 +160,7 @@
     <t>柳成荫</t>
   </si>
   <si>
-    <t>提升角色的属性二{nature2}点，被生枝时，提升卡牌的属性二4点</t>
+    <t>提升蒂娜的属性二{nature2}点，被生枝时，提升卡牌的属性二4点</t>
   </si>
   <si>
     <t>addNature(4,2)</t>
@@ -172,7 +169,7 @@
     <t>春湖倒影</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点，被生长时，获得40金币</t>
+    <t>提升蒂娜的属性一{nature1}点，被生长时，获得40金币</t>
   </si>
   <si>
     <t>addMoney(40)</t>
@@ -181,7 +178,7 @@
     <t>枯荣令</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点，下回合好感度加成减少50%</t>
+    <t>提升蒂娜的属性一{nature1}点，下回合好感度加成减少50%</t>
   </si>
   <si>
     <t>changeProperty(0.5)</t>
@@ -190,7 +187,7 @@
     <t>晨露叶</t>
   </si>
   <si>
-    <t>提升角色的属性二{nature2}点，被剪枝时，提升角色的属性三10点</t>
+    <t>提升蒂娜的属性二{nature2}点，被剪枝时，提升蒂娜的属性三10点</t>
   </si>
   <si>
     <t>addNatureAtSum(10,3)</t>
@@ -199,7 +196,7 @@
     <t>正午柳</t>
   </si>
   <si>
-    <t>提升角色的属性一{nature1}点，属性二{nature2}点，被生长时，额外触发生长6 1次</t>
+    <t>提升蒂娜的属性一{nature1}点，属性二{nature2}点，被生长时，额外触发生长6 1次</t>
   </si>
   <si>
     <t>beAdded(6,1)</t>
@@ -208,7 +205,7 @@
     <t>无心之影</t>
   </si>
   <si>
-    <t>让角色的属性一的数值等于角色的属性二</t>
+    <t>让蒂娜的属性一的数值等于蒂娜的属性二</t>
   </si>
   <si>
     <t>addNatureFromTo(1,2)</t>
@@ -1533,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I11">
         <v>20</v>
@@ -1547,7 +1544,7 @@
         <v>12003</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1573,7 +1570,7 @@
         <v>12004</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>30</v>
@@ -1585,10 +1582,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
         <v>35</v>
-      </c>
-      <c r="G13" t="s">
-        <v>36</v>
       </c>
       <c r="I13">
         <v>20</v>
@@ -1597,12 +1594,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:20">
+    <row r="14" ht="17.5" spans="1:20">
       <c r="A14">
         <v>12005</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1614,13 +1611,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I14">
         <v>20</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O14" s="4">
         <v>13</v>
@@ -1631,7 +1628,7 @@
         <v>12006</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1643,13 +1640,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I15">
         <v>20</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O15" s="4">
         <v>15</v>
@@ -1660,7 +1657,7 @@
         <v>12007</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1672,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I16">
         <v>20</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O16">
         <v>1</v>
@@ -1689,7 +1686,7 @@
         <v>12008</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -1701,13 +1698,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I17">
         <v>20</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O17" s="4">
         <v>13</v>
@@ -1718,7 +1715,7 @@
         <v>12009</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -1730,13 +1727,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I18">
         <v>20</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O18" s="4">
         <v>14</v>
@@ -1747,7 +1744,7 @@
         <v>12010</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1759,13 +1756,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I19">
         <v>20</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -1776,7 +1773,7 @@
         <v>12011</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -1788,13 +1785,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I20">
         <v>20</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O20" s="4">
         <v>2</v>
@@ -1805,22 +1802,22 @@
         <v>13001</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>60</v>
       </c>
       <c r="I21" s="1">
         <v>100</v>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="69">
   <si>
     <t>id</t>
   </si>
@@ -49,6 +49,9 @@
     <t>description</t>
   </si>
   <si>
+    <t>text</t>
+  </si>
+  <si>
     <t>trigger</t>
   </si>
   <si>
@@ -79,13 +82,22 @@
     <t>初始礼物1</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点</t>
+  </si>
+  <si>
+    <t>卡牌介绍占坑</t>
+  </si>
+  <si>
+    <t>shake(1,0.2)</t>
   </si>
   <si>
     <t>初始礼物2</t>
   </si>
   <si>
-    <t>提升蒂娜的属性二{nature2}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>magnify(0.2)</t>
   </si>
   <si>
     <t>八万霜叶</t>
@@ -97,43 +109,55 @@
     <t>根状茎</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点，属性二{nature2}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点</t>
   </si>
   <si>
     <t>雪莉牌手榨苹果汁</t>
   </si>
   <si>
-    <t>提升蒂娜的属性三{nature3}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性三{nature3}点</t>
   </si>
   <si>
     <t>诺亚牌泡腾片</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点，减少蒂娜的属性二{nature2}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，减少蒂娜的属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>shake(1,0.4)</t>
   </si>
   <si>
     <t>金圆券</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点，蒂娜的属性二{nature2}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，蒂娜的属性二{nature2}点</t>
   </si>
   <si>
     <t>新芽令</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一、二、三各{nature1}点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一、二、三各{nature1}点</t>
+  </si>
+  <si>
+    <t>magnify(0.4)</t>
   </si>
   <si>
     <t>叶缘微光</t>
   </si>
   <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点</t>
+  </si>
+  <si>
     <t>不老年轮</t>
   </si>
   <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点</t>
+  </si>
+  <si>
     <t>无心之柳</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点，减少蒂娜的属性二10点，属性二减少的数值不会改变</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，减少蒂娜的属性二10点，属性二减少的数值不会改变</t>
   </si>
   <si>
     <t>addNatureAtSum(-10,2)</t>
@@ -142,7 +166,7 @@
     <t>不眠精灵</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
   </si>
   <si>
     <t>noConsumed()</t>
@@ -151,7 +175,10 @@
     <t>永生山杨</t>
   </si>
   <si>
-    <t>提升蒂娜的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
+  </si>
+  <si>
+    <t>shake(1,0.3)</t>
   </si>
   <si>
     <t>addCard(12006,1)</t>
@@ -160,7 +187,7 @@
     <t>柳成荫</t>
   </si>
   <si>
-    <t>提升蒂娜的属性二{nature2}点，被生枝时，提升卡牌的属性二4点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被生枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升卡牌的属性二4点</t>
   </si>
   <si>
     <t>addNature(4,2)</t>
@@ -169,7 +196,7 @@
     <t>春湖倒影</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点，被生长时，获得40金币</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，被生长时，获得40金币</t>
   </si>
   <si>
     <t>addMoney(40)</t>
@@ -178,7 +205,7 @@
     <t>枯荣令</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点，下回合好感度加成减少50%</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，下回合好感度加成减少50%</t>
   </si>
   <si>
     <t>changeProperty(0.5)</t>
@@ -187,7 +214,7 @@
     <t>晨露叶</t>
   </si>
   <si>
-    <t>提升蒂娜的属性二{nature2}点，被剪枝时，提升蒂娜的属性三10点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被剪枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性三10点</t>
   </si>
   <si>
     <t>addNatureAtSum(10,3)</t>
@@ -196,7 +223,7 @@
     <t>正午柳</t>
   </si>
   <si>
-    <t>提升蒂娜的属性一{nature1}点，属性二{nature2}点，被生长时，额外触发生长6 1次</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点，被生长时，额外触发生长6 1次</t>
   </si>
   <si>
     <t>beAdded(6,1)</t>
@@ -205,10 +232,10 @@
     <t>无心之影</t>
   </si>
   <si>
-    <t>让蒂娜的属性一的数值等于蒂娜的属性二</t>
-  </si>
-  <si>
-    <t>addNatureFromTo(1,2)</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;让蒂娜的属性一的数值等于蒂娜的属性二</t>
+  </si>
+  <si>
+    <t>addNatureFromTo(1,2);magnify(0.5)</t>
   </si>
 </sst>
 </file>
@@ -230,17 +257,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -843,7 +870,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -862,7 +889,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -877,7 +913,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1191,23 +1227,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
     <col min="2" max="2" width="11.8181818181818" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.8181818181818" customWidth="1"/>
     <col min="6" max="6" width="59.4545454545455" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.2727272727273" customWidth="1"/>
-    <col min="8" max="8" width="13.6363636363636" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="18.0909090909091" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.8181818181818" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.2727272727273" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.0909090909091" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.2727272727273" customWidth="1"/>
+    <col min="9" max="9" width="13.6363636363636" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="18.0909090909091" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.8181818181818" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15" style="3" customWidth="1"/>
+    <col min="14" max="14" width="12.2727272727273" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:21">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1226,7 +1263,7 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -1235,7 +1272,7 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
@@ -1247,24 +1284,27 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4"/>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
-    </row>
-    <row r="2" spans="1:20">
+      <c r="U1" s="4"/>
+    </row>
+    <row r="2" ht="28" spans="1:21">
       <c r="A2" s="4">
         <v>11601</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="4">
         <v>4</v>
@@ -1276,31 +1316,36 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+        <v>17</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="2"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4">
+      <c r="N2" s="2"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4">
         <v>1</v>
       </c>
-      <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-    </row>
-    <row r="3" spans="1:20">
+      <c r="U2" s="4"/>
+    </row>
+    <row r="3" ht="28" spans="1:21">
       <c r="A3" s="4">
         <v>11602</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
@@ -1312,31 +1357,36 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="H3" s="8" t="s">
+        <v>22</v>
+      </c>
       <c r="I3" s="4"/>
-      <c r="J3" s="2"/>
+      <c r="J3" s="4"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4">
+      <c r="N3" s="2"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4">
         <v>1</v>
       </c>
-      <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:20">
+      <c r="U3" s="4"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:21">
       <c r="A4">
         <v>11001</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>19</v>
+      <c r="B4" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1347,22 +1397,26 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4">
+      <c r="F4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="J4">
         <v>10</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="17.5" spans="1:20">
+    <row r="5" ht="28" spans="1:21">
       <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>20</v>
+        <v>11002</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>24</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1373,22 +1427,25 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>10</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="17.5" spans="1:20">
+    <row r="6" ht="28" spans="1:21">
       <c r="A6">
         <v>11003</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>21</v>
+      <c r="B6" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1399,22 +1456,25 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6">
+      <c r="F6" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6">
         <v>10</v>
       </c>
-      <c r="O6" s="4">
+      <c r="P6" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="28" spans="1:20">
+    <row r="7" ht="28" spans="1:21">
       <c r="A7">
         <v>11004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1425,22 +1485,25 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7">
+      <c r="F7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7">
         <v>10</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:20">
+    <row r="8" ht="28" spans="1:21">
       <c r="A8">
         <v>11005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -1451,22 +1514,28 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="I8">
+      <c r="F8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8">
         <v>10</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" ht="28" spans="1:21">
       <c r="A9">
         <v>11006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1477,22 +1546,25 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9">
+      <c r="F9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9">
         <v>40</v>
       </c>
-      <c r="O9" s="4">
+      <c r="P9" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="10" ht="17.5" spans="1:20">
+    <row r="10" ht="28" spans="1:21">
       <c r="A10">
         <v>12001</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>29</v>
+      <c r="B10" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1503,22 +1575,28 @@
       <c r="E10">
         <v>2</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10">
+      <c r="F10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10">
         <v>20</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="17.5" spans="1:20">
+    <row r="11" ht="28" spans="1:21">
       <c r="A11">
         <v>12002</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>31</v>
+      <c r="B11" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -1529,22 +1607,25 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11">
+      <c r="F11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11">
         <v>20</v>
       </c>
-      <c r="O11" s="4">
+      <c r="P11" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="17.5" spans="1:20">
+    <row r="12" ht="28" spans="1:21">
       <c r="A12">
         <v>12003</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>32</v>
+      <c r="B12" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1555,22 +1636,28 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I12">
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12">
         <v>20</v>
       </c>
-      <c r="O12" s="4">
+      <c r="P12" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="13" ht="28" spans="1:20">
+    <row r="13" ht="28" spans="1:21">
       <c r="A13">
         <v>12004</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>33</v>
+      <c r="B13" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="C13">
         <v>30</v>
@@ -1581,25 +1668,28 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13">
+      <c r="F13" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13">
         <v>20</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="17.5" spans="1:20">
+    <row r="14" ht="28" spans="1:21">
       <c r="A14">
         <v>12005</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>36</v>
+      <c r="B14" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1610,25 +1700,28 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14">
+      <c r="F14" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14">
         <v>20</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O14" s="4">
+      <c r="L14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="P14" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" spans="1:20">
+    <row r="15" ht="32" customHeight="1" spans="1:21">
       <c r="A15">
         <v>12006</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>39</v>
+      <c r="B15" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1639,25 +1732,31 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15">
+      <c r="F15" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15">
         <v>20</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="O15" s="4">
+      <c r="K15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="P15" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:20">
+    <row r="16" ht="30" customHeight="1" spans="1:21">
       <c r="A16">
         <v>12007</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>42</v>
+      <c r="B16" s="9" t="s">
+        <v>51</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1668,25 +1767,28 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16">
+      <c r="F16" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16">
         <v>20</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O16">
+      <c r="M16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="17.5" spans="1:15">
+    <row r="17" ht="28" spans="1:16">
       <c r="A17">
         <v>12008</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>45</v>
+      <c r="B17" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -1697,25 +1799,28 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17">
+      <c r="F17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17">
         <v>20</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O17" s="4">
+      <c r="M17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P17" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="28" spans="1:15">
+    <row r="18" ht="28" spans="1:16">
       <c r="A18">
         <v>12009</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>48</v>
+      <c r="B18" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -1726,25 +1831,31 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18">
+      <c r="F18" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18">
         <v>20</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="O18" s="4">
+      <c r="N18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P18" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="19" ht="28" spans="1:15">
+    <row r="19" ht="42" spans="1:16">
       <c r="A19">
         <v>12010</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>51</v>
+      <c r="B19" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1755,25 +1866,28 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19">
+      <c r="F19" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19">
         <v>20</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="O19">
+      <c r="L19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P19">
         <v>10</v>
       </c>
     </row>
-    <row r="20" ht="28" spans="1:15">
+    <row r="20" ht="28" spans="1:16">
       <c r="A20">
         <v>12011</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>54</v>
+      <c r="B20" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -1784,25 +1898,28 @@
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I20">
+      <c r="F20" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20">
         <v>20</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O20" s="4">
+      <c r="M20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="P20" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="17.5" spans="1:15">
+    <row r="21" s="1" customFormat="1" ht="28" spans="1:16">
       <c r="A21" s="1">
         <v>13001</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>57</v>
+      <c r="B21" s="9" t="s">
+        <v>66</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -1813,25 +1930,28 @@
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I21" s="1">
+      <c r="F21" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="1">
         <v>100</v>
       </c>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="O21" s="4">
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="P21" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
-      <c r="F22" s="11"/>
+    <row r="22" spans="1:16">
+      <c r="F22" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -1307,7 +1307,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="4">
-        <v>4</v>
+        <v>1001</v>
       </c>
       <c r="D2" s="4">
         <v>0</v>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
   <si>
     <t>id</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>text</t>
+  </si>
+  <si>
+    <t>prompt</t>
   </si>
   <si>
     <t>trigger</t>
@@ -1227,7 +1230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
@@ -1236,15 +1239,16 @@
     <col min="6" max="6" width="59.4545454545455" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.0909090909091" style="3" customWidth="1"/>
     <col min="8" max="8" width="19.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="13.6363636363636" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="18.0909090909091" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.8181818181818" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15" style="3" customWidth="1"/>
-    <col min="14" max="14" width="12.2727272727273" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.2727272727273" customWidth="1"/>
+    <col min="10" max="10" width="13.6363636363636" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="18.0909090909091" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.8181818181818" style="3" customWidth="1"/>
+    <col min="14" max="14" width="15" style="3" customWidth="1"/>
+    <col min="15" max="15" width="12.2727272727273" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1279,7 @@
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -1287,24 +1291,27 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4"/>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
-    </row>
-    <row r="2" ht="28" spans="1:21">
+      <c r="V1" s="4"/>
+    </row>
+    <row r="2" ht="28" spans="1:22">
       <c r="A2" s="4">
         <v>11601</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="4">
         <v>1001</v>
@@ -1316,36 +1323,39 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="H2" s="7">
+        <v>4</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="J2" s="4"/>
-      <c r="K2" s="2"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4">
+      <c r="O2" s="2"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4">
         <v>1</v>
       </c>
-      <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
-    </row>
-    <row r="3" ht="28" spans="1:21">
+      <c r="V2" s="4"/>
+    </row>
+    <row r="3" ht="28" spans="1:22">
       <c r="A3" s="4">
         <v>11602</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
@@ -1357,36 +1367,39 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="4"/>
+        <v>19</v>
+      </c>
+      <c r="H3" s="8">
+        <v>4</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="J3" s="4"/>
-      <c r="K3" s="2"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4">
+      <c r="O3" s="2"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4">
         <v>1</v>
       </c>
-      <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:21">
+      <c r="V3" s="4"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:22">
       <c r="A4">
         <v>11001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1398,25 +1411,28 @@
         <v>0</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="J4">
+        <v>19</v>
+      </c>
+      <c r="H4" s="8">
+        <v>4</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="K4">
         <v>10</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:21">
+    <row r="5" ht="28" spans="1:22">
       <c r="A5">
         <v>11002</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1428,24 +1444,27 @@
         <v>0</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5">
+        <v>19</v>
+      </c>
+      <c r="H5" s="7">
+        <v>4</v>
+      </c>
+      <c r="K5">
         <v>10</v>
       </c>
-      <c r="P5" s="4">
+      <c r="Q5" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:21">
+    <row r="6" ht="28" spans="1:22">
       <c r="A6">
         <v>11003</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1457,24 +1476,27 @@
         <v>0</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6">
+        <v>19</v>
+      </c>
+      <c r="H6" s="8">
+        <v>4</v>
+      </c>
+      <c r="K6">
         <v>10</v>
       </c>
-      <c r="P6" s="4">
+      <c r="Q6" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="28" spans="1:21">
+    <row r="7" ht="28" spans="1:22">
       <c r="A7">
         <v>11004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1486,24 +1508,27 @@
         <v>2</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7">
+        <v>19</v>
+      </c>
+      <c r="H7" s="8">
+        <v>4</v>
+      </c>
+      <c r="K7">
         <v>10</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:21">
+    <row r="8" ht="28" spans="1:22">
       <c r="A8">
         <v>11005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -1515,27 +1540,30 @@
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J8">
+        <v>19</v>
+      </c>
+      <c r="H8" s="7">
+        <v>4</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8">
         <v>10</v>
       </c>
-      <c r="P8" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" ht="28" spans="1:21">
+      <c r="Q8" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:22">
       <c r="A9">
         <v>11006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1547,24 +1575,27 @@
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9">
+        <v>19</v>
+      </c>
+      <c r="H9" s="8">
+        <v>4</v>
+      </c>
+      <c r="K9">
         <v>40</v>
       </c>
-      <c r="P9" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" ht="28" spans="1:21">
+      <c r="Q9" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:22">
       <c r="A10">
         <v>12001</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1576,27 +1607,30 @@
         <v>2</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10">
+        <v>19</v>
+      </c>
+      <c r="H10" s="8">
+        <v>4</v>
+      </c>
+      <c r="I10" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10">
         <v>20</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="28" spans="1:21">
+    <row r="11" ht="28" spans="1:22">
       <c r="A11">
         <v>12002</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -1608,24 +1642,27 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11">
+        <v>19</v>
+      </c>
+      <c r="H11" s="7">
+        <v>4</v>
+      </c>
+      <c r="K11">
         <v>20</v>
       </c>
-      <c r="P11" s="4">
+      <c r="Q11" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="28" spans="1:21">
+    <row r="12" ht="28" spans="1:22">
       <c r="A12">
         <v>12003</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1637,27 +1674,30 @@
         <v>0</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12">
+        <v>19</v>
+      </c>
+      <c r="H12" s="8">
+        <v>4</v>
+      </c>
+      <c r="I12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12">
         <v>20</v>
       </c>
-      <c r="P12" s="4">
+      <c r="Q12" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="13" ht="28" spans="1:21">
+    <row r="13" ht="28" spans="1:22">
       <c r="A13">
         <v>12004</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C13">
         <v>30</v>
@@ -1669,27 +1709,30 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13">
+        <v>19</v>
+      </c>
+      <c r="H13" s="8">
+        <v>4</v>
+      </c>
+      <c r="I13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13">
         <v>20</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:21">
+    <row r="14" ht="28" spans="1:22">
       <c r="A14">
         <v>12005</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1701,27 +1744,30 @@
         <v>0</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14">
+        <v>19</v>
+      </c>
+      <c r="H14" s="7">
+        <v>4</v>
+      </c>
+      <c r="K14">
         <v>20</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="P14" s="4">
+      <c r="M14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q14" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" spans="1:21">
+    <row r="15" ht="32" customHeight="1" spans="1:22">
       <c r="A15">
         <v>12006</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1733,30 +1779,33 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" t="s">
-        <v>49</v>
-      </c>
-      <c r="J15">
+        <v>19</v>
+      </c>
+      <c r="H15" s="8">
+        <v>4</v>
+      </c>
+      <c r="I15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15">
         <v>20</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="P15" s="4">
+      <c r="L15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q15" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:21">
+    <row r="16" ht="30" customHeight="1" spans="1:22">
       <c r="A16">
         <v>12007</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1768,27 +1817,30 @@
         <v>0</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16">
+        <v>19</v>
+      </c>
+      <c r="H16" s="8">
+        <v>4</v>
+      </c>
+      <c r="K16">
         <v>20</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="P16">
+      <c r="N16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="28" spans="1:16">
+    <row r="17" ht="28" spans="1:17">
       <c r="A17">
         <v>12008</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -1800,27 +1852,30 @@
         <v>0</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17">
+        <v>19</v>
+      </c>
+      <c r="H17" s="7">
+        <v>4</v>
+      </c>
+      <c r="K17">
         <v>20</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P17" s="4">
+      <c r="N17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q17" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="28" spans="1:16">
+    <row r="18" ht="28" spans="1:17">
       <c r="A18">
         <v>12009</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -1832,30 +1887,33 @@
         <v>0</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18">
+        <v>19</v>
+      </c>
+      <c r="H18" s="8">
+        <v>4</v>
+      </c>
+      <c r="I18" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18">
         <v>20</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="P18" s="4">
+      <c r="O18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q18" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="19" ht="42" spans="1:16">
+    <row r="19" ht="42" spans="1:17">
       <c r="A19">
         <v>12010</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1867,27 +1925,30 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19">
+        <v>19</v>
+      </c>
+      <c r="H19" s="8">
+        <v>4</v>
+      </c>
+      <c r="K19">
         <v>20</v>
       </c>
-      <c r="L19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="P19">
+      <c r="M19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q19">
         <v>10</v>
       </c>
     </row>
-    <row r="20" ht="28" spans="1:16">
+    <row r="20" ht="28" spans="1:17">
       <c r="A20">
         <v>12011</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -1899,27 +1960,30 @@
         <v>0</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20">
+        <v>19</v>
+      </c>
+      <c r="H20" s="7">
+        <v>4</v>
+      </c>
+      <c r="K20">
         <v>20</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P20" s="4">
+      <c r="N20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q20" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28" spans="1:16">
+    <row r="21" s="1" customFormat="1" ht="28" spans="1:17">
       <c r="A21" s="1">
         <v>13001</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -1931,26 +1995,29 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J21" s="1">
+        <v>19</v>
+      </c>
+      <c r="H21" s="8">
+        <v>4</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="1">
         <v>100</v>
       </c>
-      <c r="K21" s="13"/>
       <c r="L21" s="13"/>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
-      <c r="P21" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="O21" s="13"/>
+      <c r="Q21" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="F22" s="14"/>
     </row>
   </sheetData>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>sale</t>
+  </si>
+  <si>
+    <t>sell</t>
   </si>
   <si>
     <t>made</t>
@@ -1230,7 +1233,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
@@ -1238,17 +1241,16 @@
     <col min="3" max="3" width="12.8181818181818" customWidth="1"/>
     <col min="6" max="6" width="59.4545454545455" style="3" customWidth="1"/>
     <col min="7" max="7" width="21.0909090909091" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.2727272727273" customWidth="1"/>
-    <col min="9" max="9" width="19.2727272727273" customWidth="1"/>
+    <col min="8" max="9" width="19.2727272727273" customWidth="1"/>
     <col min="10" max="10" width="13.6363636363636" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="18.0909090909091" style="3" customWidth="1"/>
-    <col min="13" max="13" width="14.8181818181818" style="3" customWidth="1"/>
-    <col min="14" max="14" width="15" style="3" customWidth="1"/>
-    <col min="15" max="15" width="12.2727272727273" style="3" customWidth="1"/>
+    <col min="12" max="13" width="18.0909090909091" style="3" customWidth="1"/>
+    <col min="14" max="14" width="14.8181818181818" style="3" customWidth="1"/>
+    <col min="15" max="15" width="15" style="3" customWidth="1"/>
+    <col min="16" max="16" width="12.2727272727273" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1294,24 +1296,27 @@
       <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4"/>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
       <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
     </row>
-    <row r="2" ht="28" spans="1:22">
+    <row r="2" ht="28" spans="1:23">
       <c r="A2" s="4">
         <v>11601</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4">
         <v>1001</v>
@@ -1323,39 +1328,44 @@
         <v>0</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="7">
         <v>4</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="2"/>
+      <c r="K2" s="4">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2">
+        <v>10</v>
+      </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4">
+      <c r="P2" s="2"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4">
         <v>1</v>
       </c>
-      <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
     </row>
-    <row r="3" ht="28" spans="1:22">
+    <row r="3" ht="28" spans="1:23">
       <c r="A3" s="4">
         <v>11602</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
@@ -1367,39 +1377,44 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="8">
         <v>4</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="2"/>
+      <c r="K3" s="4">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2">
+        <v>10</v>
+      </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4">
+      <c r="P3" s="2"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4">
         <v>1</v>
       </c>
-      <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:22">
+    <row r="4" ht="20" customHeight="1" spans="1:23">
       <c r="A4">
         <v>11001</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1411,10 +1426,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" s="8">
         <v>4</v>
@@ -1423,16 +1438,19 @@
       <c r="K4">
         <v>10</v>
       </c>
-      <c r="Q4">
+      <c r="L4" s="2">
+        <v>10</v>
+      </c>
+      <c r="R4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:22">
+    <row r="5" ht="28" spans="1:23">
       <c r="A5">
         <v>11002</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1444,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="7">
         <v>4</v>
@@ -1455,16 +1473,19 @@
       <c r="K5">
         <v>10</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="L5" s="2">
+        <v>10</v>
+      </c>
+      <c r="R5" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="28" spans="1:22">
+    <row r="6" ht="28" spans="1:23">
       <c r="A6">
         <v>11003</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1476,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H6" s="8">
         <v>4</v>
@@ -1487,16 +1508,19 @@
       <c r="K6">
         <v>10</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="L6" s="2">
+        <v>10</v>
+      </c>
+      <c r="R6" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="28" spans="1:22">
+    <row r="7" ht="28" spans="1:23">
       <c r="A7">
         <v>11004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1508,10 +1532,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7" s="8">
         <v>4</v>
@@ -1519,16 +1543,19 @@
       <c r="K7">
         <v>10</v>
       </c>
-      <c r="Q7">
+      <c r="L7" s="2">
+        <v>10</v>
+      </c>
+      <c r="R7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:22">
+    <row r="8" ht="28" spans="1:23">
       <c r="A8">
         <v>11005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -1540,30 +1567,33 @@
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="7">
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="L8" s="2">
+        <v>10</v>
+      </c>
+      <c r="R8" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="28" spans="1:22">
+    <row r="9" ht="28" spans="1:23">
       <c r="A9">
         <v>11006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1575,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H9" s="8">
         <v>4</v>
@@ -1586,16 +1616,19 @@
       <c r="K9">
         <v>40</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="L9" s="2">
+        <v>10</v>
+      </c>
+      <c r="R9" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="10" ht="28" spans="1:22">
+    <row r="10" ht="28" spans="1:23">
       <c r="A10">
         <v>12001</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1607,30 +1640,33 @@
         <v>2</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="8">
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K10">
         <v>20</v>
       </c>
-      <c r="Q10">
+      <c r="L10" s="2">
+        <v>10</v>
+      </c>
+      <c r="R10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="28" spans="1:22">
+    <row r="11" ht="28" spans="1:23">
       <c r="A11">
         <v>12002</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -1642,10 +1678,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" s="7">
         <v>4</v>
@@ -1653,16 +1689,19 @@
       <c r="K11">
         <v>20</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="L11" s="2">
+        <v>10</v>
+      </c>
+      <c r="R11" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="28" spans="1:22">
+    <row r="12" ht="28" spans="1:23">
       <c r="A12">
         <v>12003</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1674,30 +1713,33 @@
         <v>0</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12" s="8">
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K12">
         <v>20</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="L12" s="2">
+        <v>10</v>
+      </c>
+      <c r="R12" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="13" ht="28" spans="1:22">
+    <row r="13" ht="28" spans="1:23">
       <c r="A13">
         <v>12004</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>30</v>
@@ -1709,30 +1751,33 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" s="8">
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K13">
         <v>20</v>
       </c>
-      <c r="Q13">
+      <c r="L13" s="2">
+        <v>10</v>
+      </c>
+      <c r="R13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:22">
+    <row r="14" ht="28" spans="1:23">
       <c r="A14">
         <v>12005</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1744,10 +1789,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H14" s="7">
         <v>4</v>
@@ -1755,19 +1800,22 @@
       <c r="K14">
         <v>20</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q14" s="4">
+      <c r="L14" s="2">
+        <v>10</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R14" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1" spans="1:22">
+    <row r="15" ht="32" customHeight="1" spans="1:23">
       <c r="A15">
         <v>12006</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1779,33 +1827,36 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15" s="8">
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K15">
         <v>20</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q15" s="4">
+      <c r="L15" s="2">
+        <v>10</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="R15" s="4">
         <v>15</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:22">
+    <row r="16" ht="30" customHeight="1" spans="1:23">
       <c r="A16">
         <v>12007</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1817,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" s="8">
         <v>4</v>
@@ -1828,19 +1879,22 @@
       <c r="K16">
         <v>20</v>
       </c>
-      <c r="N16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q16">
+      <c r="L16" s="2">
+        <v>10</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="28" spans="1:17">
+    <row r="17" ht="28" spans="1:18">
       <c r="A17">
         <v>12008</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -1852,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="7">
         <v>4</v>
@@ -1863,19 +1917,22 @@
       <c r="K17">
         <v>20</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q17" s="4">
+      <c r="L17" s="2">
+        <v>10</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R17" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="28" spans="1:17">
+    <row r="18" ht="28" spans="1:18">
       <c r="A18">
         <v>12009</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -1887,33 +1944,36 @@
         <v>0</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H18" s="8">
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K18">
         <v>20</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q18" s="4">
+      <c r="L18" s="2">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="R18" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="19" ht="42" spans="1:17">
+    <row r="19" ht="42" spans="1:18">
       <c r="A19">
         <v>12010</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1925,10 +1985,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H19" s="8">
         <v>4</v>
@@ -1936,19 +1996,22 @@
       <c r="K19">
         <v>20</v>
       </c>
-      <c r="M19" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q19">
+      <c r="L19" s="2">
+        <v>10</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="R19">
         <v>10</v>
       </c>
     </row>
-    <row r="20" ht="28" spans="1:17">
+    <row r="20" ht="28" spans="1:18">
       <c r="A20">
         <v>12011</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -1960,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" s="7">
         <v>4</v>
@@ -1971,19 +2034,22 @@
       <c r="K20">
         <v>20</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q20" s="4">
+      <c r="L20" s="2">
+        <v>10</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="R20" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28" spans="1:17">
+    <row r="21" s="1" customFormat="1" ht="28" spans="1:18">
       <c r="A21" s="1">
         <v>13001</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -1995,29 +2061,32 @@
         <v>0</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" s="8">
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
       </c>
-      <c r="L21" s="13"/>
+      <c r="L21" s="2">
+        <v>10</v>
+      </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
-      <c r="Q21" s="4">
+      <c r="P21" s="13"/>
+      <c r="R21" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:18">
       <c r="F22" s="14"/>
     </row>
   </sheetData>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="83">
   <si>
     <t>id</t>
   </si>
@@ -106,7 +106,10 @@
     <t>magnify(0.2)</t>
   </si>
   <si>
-    <t>八万霜叶</t>
+    <t>可乐</t>
+  </si>
+  <si>
+    <t>一种常见的碳酸饮料</t>
   </si>
   <si>
     <t>柳荫不眠</t>
@@ -139,7 +142,7 @@
     <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，蒂娜的属性二{nature2}点</t>
   </si>
   <si>
-    <t>新芽令</t>
+    <t>棉花娃娃</t>
   </si>
   <si>
     <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一、二、三各{nature1}点</t>
@@ -151,7 +154,10 @@
     <t>叶缘微光</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点,从袋子里取出一件物品</t>
+  </si>
+  <si>
+    <t>drawCard(1)</t>
   </si>
   <si>
     <t>不老年轮</t>
@@ -193,10 +199,10 @@
     <t>柳成荫</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被生枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升卡牌的属性二4点</t>
-  </si>
-  <si>
-    <t>addNature(4,2)</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被生枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升卡牌的属性二10点</t>
+  </si>
+  <si>
+    <t>addNature(10,2)</t>
   </si>
   <si>
     <t>春湖倒影</t>
@@ -214,25 +220,25 @@
     <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，下回合好感度加成减少50%</t>
   </si>
   <si>
-    <t>changeProperty(0.5)</t>
+    <t>changeProperty(0.5);magnify(0.4)</t>
   </si>
   <si>
     <t>晨露叶</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被剪枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性三10点</t>
-  </si>
-  <si>
-    <t>addNatureAtSum(10,3)</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被剪枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性三12点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(12,3)</t>
   </si>
   <si>
     <t>正午柳</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点，被生长时，额外触发生长6 1次</t>
-  </si>
-  <si>
-    <t>beAdded(6,1)</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点，被生枝时，额外触发生长2 1次</t>
+  </si>
+  <si>
+    <t>beAdded(2,1)</t>
   </si>
   <si>
     <t>无心之影</t>
@@ -242,6 +248,36 @@
   </si>
   <si>
     <t>addNatureFromTo(1,2);magnify(0.5)</t>
+  </si>
+  <si>
+    <t>小手办</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，被制造时，获得80金币</t>
+  </si>
+  <si>
+    <t>大号棉花娃娃</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，不会被消耗</t>
+  </si>
+  <si>
+    <t>小钢笔</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点，属性三{nature3}点,被美化时，提升自身的三项属性20点</t>
+  </si>
+  <si>
+    <t>addNature(20,2);addNature(20,1);addNature(20,3);</t>
+  </si>
+  <si>
+    <t>彭格列戒指</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 被拆卸时，提升属性一40点，属性二60点，属性三40点</t>
+  </si>
+  <si>
+    <t>addNatureAtSum(40,3);addNatureAtSum(40,1);addNatureAtSum(60,2)</t>
   </si>
 </sst>
 </file>
@@ -254,7 +290,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +304,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -746,133 +788,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -910,6 +952,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -918,9 +963,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1233,16 +1275,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
     <col min="2" max="2" width="11.8181818181818" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.8181818181818" customWidth="1"/>
-    <col min="6" max="6" width="59.4545454545455" style="3" customWidth="1"/>
-    <col min="7" max="7" width="21.0909090909091" style="3" customWidth="1"/>
-    <col min="8" max="9" width="19.2727272727273" customWidth="1"/>
-    <col min="10" max="10" width="13.6363636363636" customWidth="1"/>
+    <col min="6" max="6" width="42.8181818181818" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.27272727272727" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.45454545454546" customWidth="1"/>
+    <col min="9" max="9" width="19.2727272727273" customWidth="1"/>
+    <col min="10" max="10" width="7.27272727272727" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
     <col min="12" max="13" width="18.0909090909091" style="3" customWidth="1"/>
     <col min="14" max="14" width="14.8181818181818" style="3" customWidth="1"/>
@@ -1319,7 +1362,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="4">
-        <v>1001</v>
+        <v>4</v>
       </c>
       <c r="D2" s="4">
         <v>0</v>
@@ -1344,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="L2" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1371,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" s="4">
         <v>0</v>
@@ -1393,7 +1436,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -1429,7 +1472,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H4" s="8">
         <v>4</v>
@@ -1449,8 +1492,8 @@
       <c r="A5">
         <v>11002</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>26</v>
+      <c r="B5" s="11" t="s">
+        <v>27</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1484,20 +1527,20 @@
       <c r="A6">
         <v>11003</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>27</v>
+      <c r="B6" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>20</v>
@@ -1520,7 +1563,7 @@
         <v>11004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1529,10 +1572,10 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>30</v>
+        <v>16</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>20</v>
@@ -1555,19 +1598,19 @@
         <v>11005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>12</v>
       </c>
       <c r="D8">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>32</v>
+      <c r="F8" s="12" t="s">
+        <v>33</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>20</v>
@@ -1576,7 +1619,7 @@
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1593,7 +1636,7 @@
         <v>11006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1604,8 +1647,8 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>35</v>
+      <c r="F9" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>20</v>
@@ -1628,7 +1671,7 @@
         <v>12001</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1639,8 +1682,8 @@
       <c r="E10">
         <v>2</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>37</v>
+      <c r="F10" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>20</v>
@@ -1649,7 +1692,7 @@
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K10">
         <v>20</v>
@@ -1661,12 +1704,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="28" spans="1:23">
+    <row r="11" ht="42" spans="1:23">
       <c r="A11">
         <v>12002</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>39</v>
+      <c r="B11" s="11" t="s">
+        <v>40</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -1677,14 +1720,17 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>40</v>
+      <c r="F11" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="7">
         <v>4</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
       </c>
       <c r="K11">
         <v>20</v>
@@ -1700,20 +1746,20 @@
       <c r="A12">
         <v>12003</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>41</v>
+      <c r="B12" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>42</v>
+      <c r="F12" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>20</v>
@@ -1722,7 +1768,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K12">
         <v>20</v>
@@ -1734,15 +1780,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" ht="28" spans="1:23">
+    <row r="13" ht="42" spans="1:23">
       <c r="A13">
         <v>12004</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>43</v>
+      <c r="B13" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -1750,8 +1796,8 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>44</v>
+      <c r="F13" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>20</v>
@@ -1760,7 +1806,7 @@
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K13">
         <v>20</v>
@@ -1776,11 +1822,11 @@
       <c r="A14">
         <v>12005</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>46</v>
+      <c r="B14" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1788,8 +1834,8 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>47</v>
+      <c r="F14" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>20</v>
@@ -1804,7 +1850,7 @@
         <v>10</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R14" s="4">
         <v>13</v>
@@ -1814,8 +1860,8 @@
       <c r="A15">
         <v>12006</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>49</v>
+      <c r="B15" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1826,8 +1872,8 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>50</v>
+      <c r="F15" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>20</v>
@@ -1836,7 +1882,7 @@
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K15">
         <v>20</v>
@@ -1845,7 +1891,7 @@
         <v>10</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R15" s="4">
         <v>15</v>
@@ -1855,8 +1901,8 @@
       <c r="A16">
         <v>12007</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>53</v>
+      <c r="B16" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1867,8 +1913,8 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>54</v>
+      <c r="F16" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>20</v>
@@ -1883,7 +1929,7 @@
         <v>10</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -1893,8 +1939,8 @@
       <c r="A17">
         <v>12008</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>56</v>
+      <c r="B17" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -1905,8 +1951,8 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>57</v>
+      <c r="F17" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>20</v>
@@ -1921,7 +1967,7 @@
         <v>10</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R17" s="4">
         <v>13</v>
@@ -1931,8 +1977,8 @@
       <c r="A18">
         <v>12009</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>59</v>
+      <c r="B18" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -1943,8 +1989,8 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>60</v>
+      <c r="F18" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>20</v>
@@ -1953,39 +1999,36 @@
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K18">
         <v>20</v>
       </c>
       <c r="L18" s="2">
         <v>10</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>61</v>
       </c>
       <c r="R18" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="19" ht="42" spans="1:18">
+    <row r="19" ht="56" spans="1:18">
       <c r="A19">
         <v>12010</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>62</v>
+      <c r="B19" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>63</v>
+      <c r="F19" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>20</v>
@@ -2000,30 +2043,30 @@
         <v>10</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R19">
         <v>10</v>
       </c>
     </row>
-    <row r="20" ht="28" spans="1:18">
+    <row r="20" ht="42" spans="1:18">
       <c r="A20">
         <v>12011</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>65</v>
+      <c r="B20" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>66</v>
+      <c r="F20" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>20</v>
@@ -2037,8 +2080,8 @@
       <c r="L20" s="2">
         <v>10</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>67</v>
+      <c r="M20" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="R20" s="4">
         <v>2</v>
@@ -2048,8 +2091,8 @@
       <c r="A21" s="1">
         <v>13001</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>68</v>
+      <c r="B21" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -2060,8 +2103,8 @@
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>69</v>
+      <c r="F21" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>20</v>
@@ -2070,7 +2113,7 @@
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K21" s="1">
         <v>100</v>
@@ -2078,16 +2121,118 @@
       <c r="L21" s="2">
         <v>10</v>
       </c>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
       <c r="R21" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
-      <c r="F22" s="14"/>
+    <row r="22" customFormat="1" ht="26" spans="1:18">
+      <c r="A22" s="1">
+        <v>13002</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22">
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22"/>
+      <c r="M22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" ht="28" spans="1:18">
+      <c r="A23" s="1">
+        <v>13003</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>42</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" ht="56" spans="1:18">
+      <c r="A24" s="1">
+        <v>13004</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24">
+        <v>10</v>
+      </c>
+      <c r="D24">
+        <v>10</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" ht="70" spans="1:18">
+      <c r="A25" s="1">
+        <v>13005</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>82</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -199,7 +199,7 @@
     <t>柳成荫</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被生枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升卡牌的属性二10点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被生枝时，提升卡牌的属性二10点</t>
   </si>
   <si>
     <t>addNature(10,2)</t>
@@ -462,7 +462,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,6 +472,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -794,7 +800,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -818,16 +824,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
@@ -836,89 +842,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -963,6 +969,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1384,10 +1393,11 @@
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L2" s="2">
-        <v>1</v>
+        <f>K2*0.8</f>
+        <v>8</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1433,10 +1443,11 @@
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L3" s="2">
-        <v>1</v>
+        <f t="shared" ref="L3:L16" si="0">K3*0.8</f>
+        <v>8</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -1479,10 +1490,11 @@
       </c>
       <c r="I4" s="8"/>
       <c r="K4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="R4">
         <v>2</v>
@@ -1514,10 +1526,11 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L5" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="R5" s="4">
         <v>2</v>
@@ -1549,10 +1562,11 @@
         <v>4</v>
       </c>
       <c r="K6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L6" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="R6" s="4">
         <v>3</v>
@@ -1584,16 +1598,17 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L7" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="R7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="28" spans="1:23">
+    <row r="8" ht="42" spans="1:23">
       <c r="A8">
         <v>11005</v>
       </c>
@@ -1622,10 +1637,11 @@
         <v>34</v>
       </c>
       <c r="K8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L8" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="R8" s="4">
         <v>4</v>
@@ -1657,10 +1673,10 @@
         <v>4</v>
       </c>
       <c r="K9">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L9" s="2">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="R9" s="4">
         <v>4</v>
@@ -1695,10 +1711,11 @@
         <v>39</v>
       </c>
       <c r="K10">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L10" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="R10">
         <v>2</v>
@@ -1733,10 +1750,11 @@
         <v>42</v>
       </c>
       <c r="K11">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L11" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="R11" s="4">
         <v>10</v>
@@ -1771,10 +1789,11 @@
         <v>39</v>
       </c>
       <c r="K12">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L12" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="R12" s="4">
         <v>11</v>
@@ -1809,16 +1828,17 @@
         <v>47</v>
       </c>
       <c r="K13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L13" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="R13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:23">
+    <row r="14" ht="42" spans="1:23">
       <c r="A14">
         <v>12005</v>
       </c>
@@ -1843,14 +1863,15 @@
       <c r="H14" s="7">
         <v>4</v>
       </c>
+      <c r="I14" t="s">
+        <v>50</v>
+      </c>
       <c r="K14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L14" s="2">
-        <v>10</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>50</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="R14" s="4">
         <v>13</v>
@@ -1885,10 +1906,11 @@
         <v>53</v>
       </c>
       <c r="K15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L15" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>54</v>
@@ -1908,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1923,10 +1945,11 @@
         <v>4</v>
       </c>
       <c r="K16">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L16" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>57</v>
@@ -1961,10 +1984,11 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L17" s="2">
-        <v>10</v>
+        <f>K17*0.8</f>
+        <v>32</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>60</v>
@@ -2002,10 +2026,11 @@
         <v>63</v>
       </c>
       <c r="K18">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L18" s="2">
-        <v>10</v>
+        <f>K18*0.8</f>
+        <v>32</v>
       </c>
       <c r="R18" s="4">
         <v>14</v>
@@ -2037,10 +2062,11 @@
         <v>4</v>
       </c>
       <c r="K19">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L19" s="2">
-        <v>10</v>
+        <f>K19*0.8</f>
+        <v>32</v>
       </c>
       <c r="N19" s="3" t="s">
         <v>66</v>
@@ -2075,10 +2101,11 @@
         <v>4</v>
       </c>
       <c r="K20">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L20" s="2">
-        <v>10</v>
+        <f>K20*0.8</f>
+        <v>32</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>69</v>
@@ -2116,10 +2143,11 @@
         <v>72</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L21" s="2">
-        <v>10</v>
+        <f>K21*0.8</f>
+        <v>64</v>
       </c>
       <c r="M21" s="14"/>
       <c r="N21" s="14"/>
@@ -2152,6 +2180,13 @@
         <v>20</v>
       </c>
       <c r="H22"/>
+      <c r="K22">
+        <v>80</v>
+      </c>
+      <c r="L22" s="2">
+        <f>K22*0.8</f>
+        <v>64</v>
+      </c>
       <c r="M22" t="s">
         <v>60</v>
       </c>
@@ -2178,8 +2213,15 @@
       <c r="G23" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="I23" t="s">
         <v>50</v>
+      </c>
+      <c r="K23" s="15">
+        <v>80</v>
+      </c>
+      <c r="L23" s="2">
+        <f>K23*0.8</f>
+        <v>64</v>
       </c>
     </row>
     <row r="24" ht="56" spans="1:18">
@@ -2204,6 +2246,13 @@
       <c r="G24" s="6" t="s">
         <v>20</v>
       </c>
+      <c r="K24">
+        <v>80</v>
+      </c>
+      <c r="L24" s="2">
+        <f>K24*0.8</f>
+        <v>64</v>
+      </c>
       <c r="O24" s="3" t="s">
         <v>79</v>
       </c>
@@ -2229,6 +2278,13 @@
       </c>
       <c r="G25" s="6" t="s">
         <v>20</v>
+      </c>
+      <c r="K25" s="15">
+        <v>80</v>
+      </c>
+      <c r="L25" s="2">
+        <f>K25*0.8</f>
+        <v>64</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>82</v>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="109">
   <si>
     <t>id</t>
   </si>
@@ -85,52 +85,84 @@
     <t>dialog</t>
   </si>
   <si>
-    <t>初始礼物1</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点</t>
-  </si>
-  <si>
-    <t>卡牌介绍占坑</t>
+    <t>像素风挂件</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点</t>
+  </si>
+  <si>
+    <t>一个8-bit风格的粉色头发小人，像游戏的她。</t>
   </si>
   <si>
     <t>shake(1,0.2)</t>
   </si>
   <si>
-    <t>初始礼物2</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日式风铃</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>声音清冽，有风吹来时就会叮咚作响。</t>
   </si>
   <si>
     <t>magnify(0.2)</t>
   </si>
   <si>
-    <t>可乐</t>
-  </si>
-  <si>
-    <t>一种常见的碳酸饮料</t>
-  </si>
-  <si>
-    <t>柳荫不眠</t>
-  </si>
-  <si>
-    <t>根状茎</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点</t>
+    <t xml:space="preserve"> 折纸书签</t>
+  </si>
+  <si>
+    <t>折成可爱动物形状的书签，可惜蒂娜不经常看书</t>
+  </si>
+  <si>
+    <t>迷你食物模型</t>
+  </si>
+  <si>
+    <t>可以捧在手心里的超小汉堡模型,让人食欲满满</t>
+  </si>
+  <si>
+    <t>星星兔挂坠</t>
+  </si>
+  <si>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>毛茸茸的兔子抱着星星，让人想捏一捏，感觉会很适合蒂娜的包</t>
   </si>
   <si>
     <t>雪莉牌手榨苹果汁</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性三{nature3}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性三{nature3}点</t>
+  </si>
+  <si>
+    <t>似乎是某位具有巨力的魔法少女亲手制作的果汁？</t>
   </si>
   <si>
     <t>诺亚牌泡腾片</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，减少蒂娜的属性二{nature2}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，减少蒂娜的属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>一款风味独特的泡腾片，深受年轻人市场青睐</t>
   </si>
   <si>
     <t>shake(1,0.4)</t>
@@ -139,55 +171,93 @@
     <t>金圆券</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，蒂娜的属性二{nature2}点</t>
+    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，蒂娜的属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>看起来普通的失效货币，但他的价值似乎比想象中要高</t>
   </si>
   <si>
     <t>棉花娃娃</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一、二、三各{nature1}点</t>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一、二、三各{nature1}点</t>
+  </si>
+  <si>
+    <t>acg爱好者经常会挂在包间的角色q版娃娃，蒂娜应该会觉得这很可爱</t>
   </si>
   <si>
     <t>magnify(0.4)</t>
   </si>
   <si>
-    <t>叶缘微光</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点,从袋子里取出一件物品</t>
+    <t xml:space="preserve"> 皮质相机肩带</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，属性二{nature2}点,从袋子里取出一件物品</t>
+  </si>
+  <si>
+    <t>内侧有手工雕刻的复古花纹，能减轻脖子的负担。</t>
   </si>
   <si>
     <t>drawCard(1)</t>
   </si>
   <si>
-    <t>不老年轮</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点</t>
-  </si>
-  <si>
-    <t>无心之柳</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，减少蒂娜的属性二10点，属性二减少的数值不会改变</t>
+    <t xml:space="preserve"> 水下摄影袋</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点</t>
+  </si>
+  <si>
+    <t>让相机也能在泳池里工作，打开新世界大门。</t>
+  </si>
+  <si>
+    <t>麻薯捏捏乐</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，减少蒂娜的属性二10点，属性二减少的数值不会改变</t>
+  </si>
+  <si>
+    <t>手感像刚捣好的年糕，治愈强迫症。</t>
   </si>
   <si>
     <t>addNatureAtSum(-10,2)</t>
   </si>
   <si>
-    <t>不眠精灵</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蓝莓巧克力</t>
+    </r>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
+  </si>
+  <si>
+    <t>整颗冻干蓝莓外面裹着白巧克力，酸甜融合，蒂娜肯定会很喜欢</t>
   </si>
   <si>
     <t>noConsumed()</t>
   </si>
   <si>
-    <t>永生山杨</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
+    <t>魔法少女变身器</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
+  </si>
+  <si>
+    <t>按下会发光并播放音乐的小玩具，哪个女孩能拒绝？</t>
   </si>
   <si>
     <t>shake(1,0.3)</t>
@@ -196,76 +266,103 @@
     <t>addCard(12006,1)</t>
   </si>
   <si>
-    <t>柳成荫</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被生枝时，提升卡牌的属性二10点</t>
+    <t>索引标签贴</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点，被生枝时，提升卡牌的属性二10点</t>
+  </si>
+  <si>
+    <t>半透明磨砂材质，方便分类标记</t>
   </si>
   <si>
     <t>addNature(10,2)</t>
   </si>
   <si>
-    <t>春湖倒影</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，被生长时，获得40金币</t>
+    <t>异形回形针</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，被生长时，获得40金币</t>
+  </si>
+  <si>
+    <t>被做成了云朵或小飞机的形状，夹在相册上很可爱。</t>
   </si>
   <si>
     <t>addMoney(40)</t>
   </si>
   <si>
-    <t>枯荣令</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，下回合好感度加成减少50%</t>
+    <t>解压魔方</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，下回合好感度加成减少50%</t>
+  </si>
+  <si>
+    <t>金属材质，手感沉甸甸，转动时有种冰冷顺滑的机械感，感觉蒂娜会玩不来</t>
   </si>
   <si>
     <t>changeProperty(0.5);magnify(0.4)</t>
   </si>
   <si>
-    <t>晨露叶</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，被剪枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性三12点</t>
+    <t>隔音耳罩</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点，被剪枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性三12点</t>
+  </si>
+  <si>
+    <t>在嘈杂环境中制造绝对安静的小世界，集中精神必备。</t>
   </si>
   <si>
     <t>addNatureAtSum(12,3)</t>
   </si>
   <si>
-    <t>正午柳</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点，被生枝时，额外触发生长2 1次</t>
+    <t>扭蛋机存钱罐</t>
+  </si>
+  <si>
+    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，属性二{nature2}点，被生枝时，额外触发生长2 1次</t>
+  </si>
+  <si>
+    <t>投币进去就能扭，应该会让存钱变得很快乐。</t>
   </si>
   <si>
     <t>beAdded(2,1)</t>
   </si>
   <si>
-    <t>无心之影</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;让蒂娜的属性一的数值等于蒂娜的属性二</t>
+    <t>平衡摆件</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 让蒂娜的属性一的数值等于蒂娜的属性二</t>
+  </si>
+  <si>
+    <t>一个看似能永动的装置，看着它能看很久，像被催眠。</t>
   </si>
   <si>
     <t>addNatureFromTo(1,2);magnify(0.5)</t>
   </si>
   <si>
-    <t>小手办</t>
-  </si>
-  <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，被制造时，获得80金币</t>
+    <t>发光水母瓶</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，被制造时，获得80金币</t>
+  </si>
+  <si>
+    <t>黑暗中会发出梦幻的蓝光，像把一小片海带回家。</t>
   </si>
   <si>
     <t>大号棉花娃娃</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性二{nature2}点，不会被消耗</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点，不会被消耗</t>
+  </si>
+  <si>
+    <t>大小很夸张的棉花娃娃，是死忠粉才会想要的物品</t>
   </si>
   <si>
     <t>小钢笔</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 提升蒂娜的属性一{nature1}点，属性二{nature2}点，属性三{nature3}点,被美化时，提升自身的三项属性20点</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，属性二{nature2}点，属性三{nature3}点,被美化时，提升自身的三项属性20点</t>
+  </si>
+  <si>
+    <t>一只看似普通的钢笔</t>
   </si>
   <si>
     <t>addNature(20,2);addNature(20,1);addNature(20,3);</t>
@@ -274,10 +371,25 @@
     <t>彭格列戒指</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 被拆卸时，提升属性一40点，属性二60点，属性三40点</t>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  被拆卸时，提升属性一40点，属性二60点，属性三40点</t>
+  </si>
+  <si>
+    <t>似乎是某个意大利黑手党派的重要物品，拥有强大的力量</t>
   </si>
   <si>
     <t>addNatureAtSum(40,3);addNatureAtSum(40,1);addNatureAtSum(60,2)</t>
+  </si>
+  <si>
+    <t>大盲盒</t>
+  </si>
+  <si>
+    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  随机获得3张罕见礼物牌</t>
+  </si>
+  <si>
+    <t>商场里售卖的盲盒，不知道里面会开出什么东西</t>
+  </si>
+  <si>
+    <t>addRandomCard(1,2,3)</t>
   </si>
 </sst>
 </file>
@@ -299,6 +411,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -309,12 +427,6 @@
       <sz val="12"/>
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -943,22 +1055,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1284,14 +1396,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13.5454545454545" customWidth="1"/>
     <col min="2" max="2" width="11.8181818181818" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.8181818181818" customWidth="1"/>
     <col min="6" max="6" width="42.8181818181818" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.27272727272727" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.4545454545455" customWidth="1"/>
     <col min="8" max="8" width="9.45454545454546" customWidth="1"/>
     <col min="9" max="9" width="19.2727272727273" customWidth="1"/>
     <col min="10" max="10" width="7.27272727272727" customWidth="1"/>
@@ -1321,7 +1433,7 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -1417,7 +1529,7 @@
       <c r="A3" s="4">
         <v>11602</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="4">
@@ -1432,21 +1544,21 @@
       <c r="F3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" s="8">
-        <v>4</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>24</v>
+      </c>
+      <c r="H3" s="4">
+        <v>4</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4">
         <v>10</v>
       </c>
       <c r="L3" s="2">
-        <f t="shared" ref="L3:L16" si="0">K3*0.8</f>
+        <f t="shared" ref="L3:L25" si="0">K3*0.8</f>
         <v>8</v>
       </c>
       <c r="M3" s="2"/>
@@ -1467,8 +1579,8 @@
       <c r="A4">
         <v>11001</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>25</v>
+      <c r="B4" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1482,13 +1594,13 @@
       <c r="F4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="8">
-        <v>4</v>
-      </c>
-      <c r="I4" s="8"/>
+      <c r="G4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="4">
+        <v>4</v>
+      </c>
+      <c r="I4" s="9"/>
       <c r="K4">
         <v>20</v>
       </c>
@@ -1504,8 +1616,8 @@
       <c r="A5">
         <v>11002</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>27</v>
+      <c r="B5" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1519,8 +1631,8 @@
       <c r="F5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>20</v>
+      <c r="G5" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="H5" s="7">
         <v>4</v>
@@ -1540,8 +1652,8 @@
       <c r="A6">
         <v>11003</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>28</v>
+      <c r="B6" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1553,12 +1665,12 @@
         <v>0</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="8">
+        <v>31</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="4">
         <v>4</v>
       </c>
       <c r="K6">
@@ -1577,7 +1689,7 @@
         <v>11004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1589,12 +1701,12 @@
         <v>16</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="8">
+        <v>34</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="4">
         <v>4</v>
       </c>
       <c r="K7">
@@ -1613,7 +1725,7 @@
         <v>11005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -1625,16 +1737,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="H8" s="7">
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K8">
         <v>20</v>
@@ -1647,12 +1759,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="28" spans="1:23">
+    <row r="9" ht="42" spans="1:23">
       <c r="A9">
         <v>11006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1664,12 +1776,12 @@
         <v>0</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="8">
+        <v>41</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="9">
         <v>4</v>
       </c>
       <c r="K9">
@@ -1686,8 +1798,8 @@
       <c r="A10">
         <v>12001</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>37</v>
+      <c r="B10" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1699,16 +1811,16 @@
         <v>2</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="8">
+        <v>44</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="9">
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K10">
         <v>40</v>
@@ -1725,8 +1837,8 @@
       <c r="A11">
         <v>12002</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>40</v>
+      <c r="B11" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -1738,16 +1850,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>20</v>
+        <v>48</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="H11" s="7">
         <v>4</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K11">
         <v>40</v>
@@ -1764,8 +1876,8 @@
       <c r="A12">
         <v>12003</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>43</v>
+      <c r="B12" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1777,16 +1889,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="8">
+        <v>53</v>
+      </c>
+      <c r="H12" s="9">
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K12">
         <v>40</v>
@@ -1803,8 +1915,8 @@
       <c r="A13">
         <v>12004</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>45</v>
+      <c r="B13" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="C13">
         <v>24</v>
@@ -1816,16 +1928,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="8">
+        <v>56</v>
+      </c>
+      <c r="H13" s="9">
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="K13">
         <v>40</v>
@@ -1842,8 +1954,8 @@
       <c r="A14">
         <v>12005</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>48</v>
+      <c r="B14" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1855,16 +1967,16 @@
         <v>0</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>20</v>
+        <v>59</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="H14" s="7">
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K14">
         <v>40</v>
@@ -1881,8 +1993,8 @@
       <c r="A15">
         <v>12006</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>51</v>
+      <c r="B15" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1894,16 +2006,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="8">
+        <v>63</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="9">
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="K15">
         <v>40</v>
@@ -1913,7 +2025,7 @@
         <v>32</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="R15" s="4">
         <v>15</v>
@@ -1923,8 +2035,8 @@
       <c r="A16">
         <v>12007</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>55</v>
+      <c r="B16" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1936,12 +2048,12 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="8">
+        <v>68</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="9">
         <v>4</v>
       </c>
       <c r="K16">
@@ -1952,7 +2064,7 @@
         <v>32</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -1962,8 +2074,8 @@
       <c r="A17">
         <v>12008</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>58</v>
+      <c r="B17" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -1975,10 +2087,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>20</v>
+        <v>72</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="H17" s="7">
         <v>4</v>
@@ -1987,22 +2099,22 @@
         <v>40</v>
       </c>
       <c r="L17" s="2">
-        <f>K17*0.8</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="R17" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="28" spans="1:18">
+    <row r="18" ht="42" spans="1:18">
       <c r="A18">
         <v>12009</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>61</v>
+      <c r="B18" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -2014,22 +2126,22 @@
         <v>0</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="8">
+        <v>76</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="9">
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="K18">
         <v>40</v>
       </c>
       <c r="L18" s="2">
-        <f>K18*0.8</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="R18" s="4">
@@ -2040,8 +2152,8 @@
       <c r="A19">
         <v>12010</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>64</v>
+      <c r="B19" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2053,23 +2165,23 @@
         <v>0</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="8">
+        <v>81</v>
+      </c>
+      <c r="H19" s="9">
         <v>4</v>
       </c>
       <c r="K19">
         <v>40</v>
       </c>
       <c r="L19" s="2">
-        <f>K19*0.8</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="R19">
         <v>10</v>
@@ -2079,8 +2191,8 @@
       <c r="A20">
         <v>12011</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>67</v>
+      <c r="B20" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -2092,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>20</v>
+        <v>84</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="H20" s="7">
         <v>4</v>
@@ -2104,11 +2216,11 @@
         <v>40</v>
       </c>
       <c r="L20" s="2">
-        <f>K20*0.8</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="R20" s="4">
         <v>2</v>
@@ -2118,8 +2230,8 @@
       <c r="A21" s="1">
         <v>13001</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>70</v>
+      <c r="B21" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="C21" s="1">
         <v>0</v>
@@ -2131,22 +2243,22 @@
         <v>0</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="8">
+        <v>88</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="9">
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="K21" s="1">
         <v>80</v>
       </c>
       <c r="L21" s="2">
-        <f>K21*0.8</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="M21" s="14"/>
@@ -2157,12 +2269,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" customFormat="1" ht="26" spans="1:18">
+    <row r="22" customFormat="1" ht="17.5" spans="1:18">
       <c r="A22" s="1">
         <v>13002</v>
       </c>
-      <c r="B22" t="s">
-        <v>73</v>
+      <c r="B22" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -2174,21 +2286,21 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="H22"/>
       <c r="K22">
         <v>80</v>
       </c>
       <c r="L22" s="2">
-        <f>K22*0.8</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="M22" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:18">
@@ -2196,7 +2308,7 @@
         <v>13003</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2208,19 +2320,19 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>20</v>
+        <v>95</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="I23" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K23" s="15">
         <v>80</v>
       </c>
       <c r="L23" s="2">
-        <f>K23*0.8</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
     </row>
@@ -2229,7 +2341,7 @@
         <v>13004</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2241,20 +2353,20 @@
         <v>1</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>20</v>
+        <v>98</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="K24">
         <v>80</v>
       </c>
       <c r="L24" s="2">
-        <f>K24*0.8</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" ht="70" spans="1:18">
@@ -2262,7 +2374,7 @@
         <v>13005</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2274,20 +2386,53 @@
         <v>0</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>20</v>
+        <v>102</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="K25" s="15">
         <v>80</v>
       </c>
       <c r="L25" s="2">
-        <f>K25*0.8</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>82</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="42" spans="1:18">
+      <c r="A26" s="1">
+        <v>13006</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="N26" s="1">
+        <v>80</v>
+      </c>
+      <c r="O26">
+        <f>N26*0.8</f>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
   <si>
     <t>id</t>
   </si>
@@ -85,48 +85,25 @@
     <t>dialog</t>
   </si>
   <si>
-    <t>像素风挂件</t>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点</t>
-  </si>
-  <si>
-    <t>一个8-bit风格的粉色头发小人，像游戏的她。</t>
+    <t>蓝色千纸鹤</t>
+  </si>
+  <si>
+    <t>提升蒂娜的好感一{nature1}点</t>
   </si>
   <si>
     <t>shake(1,0.2)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0F1115"/>
-        <rFont val="Segoe UI"/>
-        <charset val="134"/>
-      </rPr>
-      <t>日式风铃</t>
-    </r>
-  </si>
-  <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点</t>
-  </si>
-  <si>
-    <t>声音清冽，有风吹来时就会叮咚作响。</t>
+    <t>黄色千纸鹤</t>
+  </si>
+  <si>
+    <t>提升蒂娜的好感二{nature2}点</t>
   </si>
   <si>
     <t>magnify(0.2)</t>
   </si>
   <si>
-    <t xml:space="preserve"> 折纸书签</t>
+    <t>折纸书签</t>
   </si>
   <si>
     <t>折成可爱动物形状的书签，可惜蒂娜不经常看书</t>
@@ -141,7 +118,7 @@
     <t>星星兔挂坠</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，属性二{nature2}点</t>
+    <t>提升蒂娜的好感一{nature1}点，好感二{nature2}点</t>
   </si>
   <si>
     <t>毛茸茸的兔子抱着星星，让人想捏一捏，感觉会很适合蒂娜的包</t>
@@ -150,7 +127,7 @@
     <t>雪莉牌手榨苹果汁</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性三{nature3}点</t>
+    <t>提升蒂娜的好感三{nature3}点</t>
   </si>
   <si>
     <t>似乎是某位具有巨力的魔法少女亲手制作的果汁？</t>
@@ -159,7 +136,7 @@
     <t>诺亚牌泡腾片</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，减少蒂娜的属性二{nature2}点</t>
+    <t>提升蒂娜的好感一{nature1}点，减少蒂娜的好感二{nature2}点</t>
   </si>
   <si>
     <t>一款风味独特的泡腾片，深受年轻人市场青睐</t>
@@ -171,7 +148,7 @@
     <t>金圆券</t>
   </si>
   <si>
-    <t>&lt;color=grey&gt;&lt;b&gt;普通&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，蒂娜的属性二{nature2}点</t>
+    <t>提升蒂娜的好感一{nature1}点，蒂娜的好感二{nature2}点</t>
   </si>
   <si>
     <t>看起来普通的失效货币，但他的价值似乎比想象中要高</t>
@@ -180,7 +157,7 @@
     <t>棉花娃娃</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一、二、三各{nature1}点</t>
+    <t>提升蒂娜的好感一、二、三各{nature1}点</t>
   </si>
   <si>
     <t>acg爱好者经常会挂在包间的角色q版娃娃，蒂娜应该会觉得这很可爱</t>
@@ -189,10 +166,10 @@
     <t>magnify(0.4)</t>
   </si>
   <si>
-    <t xml:space="preserve"> 皮质相机肩带</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，属性二{nature2}点,从袋子里取出一件物品</t>
+    <t>皮质相机肩带</t>
+  </si>
+  <si>
+    <t>提升蒂娜的好感一{nature1}点，好感二{nature2}点,从袋子里取出一件物品</t>
   </si>
   <si>
     <t>内侧有手工雕刻的复古花纹，能减轻脖子的负担。</t>
@@ -201,10 +178,7 @@
     <t>drawCard(1)</t>
   </si>
   <si>
-    <t xml:space="preserve"> 水下摄影袋</t>
-  </si>
-  <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点</t>
+    <t>水下摄影袋</t>
   </si>
   <si>
     <t>让相机也能在泳池里工作，打开新世界大门。</t>
@@ -213,7 +187,7 @@
     <t>麻薯捏捏乐</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，减少蒂娜的属性二10点，属性二减少的数值不会改变</t>
+    <t>提升蒂娜的好感一{nature1}点，减少蒂娜的好感二10点，好感二减少的数值不会改变</t>
   </si>
   <si>
     <t>手感像刚捣好的年糕，治愈强迫症。</t>
@@ -242,7 +216,7 @@
     </r>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，当此牌被剪枝时，不会被消耗</t>
+    <t>提升蒂娜的好感一{nature1}点，当此牌被剪枝时，不会被消耗</t>
   </si>
   <si>
     <t>整颗冻干蓝莓外面裹着白巧克力，酸甜融合，蒂娜肯定会很喜欢</t>
@@ -254,7 +228,7 @@
     <t>魔法少女变身器</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
+    <t>提升蒂娜的好感二{nature2}点，当此牌被生枝时，往手牌中额外加入一张此卡</t>
   </si>
   <si>
     <t>按下会发光并播放音乐的小玩具，哪个女孩能拒绝？</t>
@@ -269,7 +243,7 @@
     <t>索引标签贴</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点，被生枝时，提升卡牌的属性二10点</t>
+    <t>提升蒂娜的好感二{nature2}点，被生枝时，提升卡牌的好感二10点</t>
   </si>
   <si>
     <t>半透明磨砂材质，方便分类标记</t>
@@ -281,7 +255,7 @@
     <t>异形回形针</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，被生长时，获得40金币</t>
+    <t>提升蒂娜的好感一{nature1}点，被生长时，获得40金币</t>
   </si>
   <si>
     <t>被做成了云朵或小飞机的形状，夹在相册上很可爱。</t>
@@ -293,7 +267,7 @@
     <t>解压魔方</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，下回合好感度加成减少50%</t>
+    <t>提升蒂娜的好感一{nature1}点，下回合好感度加成减少50%</t>
   </si>
   <si>
     <t>金属材质，手感沉甸甸，转动时有种冰冷顺滑的机械感，感觉蒂娜会玩不来</t>
@@ -305,7 +279,7 @@
     <t>隔音耳罩</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点，被剪枝时，&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性三12点</t>
+    <t>提升蒂娜的好感二{nature2}点，被剪枝时，提升蒂娜的好感三12点</t>
   </si>
   <si>
     <t>在嘈杂环境中制造绝对安静的小世界，集中精神必备。</t>
@@ -317,7 +291,7 @@
     <t>扭蛋机存钱罐</t>
   </si>
   <si>
-    <t>&lt;color=blue&gt;&lt;b&gt;罕见&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，属性二{nature2}点，被生枝时，额外触发生长2 1次</t>
+    <t>提升蒂娜的好感一{nature1}点，好感二{nature2}点，被生枝时，额外触发生长21次</t>
   </si>
   <si>
     <t>投币进去就能扭，应该会让存钱变得很快乐。</t>
@@ -329,7 +303,7 @@
     <t>平衡摆件</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt; 让蒂娜的属性一的数值等于蒂娜的属性二</t>
+    <t>让蒂娜的好感一的数值等于蒂娜的好感二</t>
   </si>
   <si>
     <t>一个看似能永动的装置，看着它能看很久，像被催眠。</t>
@@ -341,7 +315,7 @@
     <t>发光水母瓶</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，被制造时，获得80金币</t>
+    <t>提升蒂娜的好感一{nature1}点，被制造时，获得80金币</t>
   </si>
   <si>
     <t>黑暗中会发出梦幻的蓝光，像把一小片海带回家。</t>
@@ -350,7 +324,7 @@
     <t>大号棉花娃娃</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性二{nature2}点，不会被消耗</t>
+    <t>提升蒂娜的好感二{nature2}点，不会被消耗</t>
   </si>
   <si>
     <t>大小很夸张的棉花娃娃，是死忠粉才会想要的物品</t>
@@ -359,7 +333,7 @@
     <t>小钢笔</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  提升蒂娜的属性一{nature1}点，属性二{nature2}点，属性三{nature3}点,被美化时，提升自身的三项属性20点</t>
+    <t>提升蒂娜的好感一{nature1}点，好感二{nature2}点，好感三{nature3}点,被美化时，提升自身的三项好感20点</t>
   </si>
   <si>
     <t>一只看似普通的钢笔</t>
@@ -371,7 +345,7 @@
     <t>彭格列戒指</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  被拆卸时，提升属性一40点，属性二60点，属性三40点</t>
+    <t>被拆卸时，提升好感一40点，好感二60点，好感三40点</t>
   </si>
   <si>
     <t>似乎是某个意大利黑手党派的重要物品，拥有强大的力量</t>
@@ -383,7 +357,7 @@
     <t>大盲盒</t>
   </si>
   <si>
-    <t>&lt;color=yellow&gt;&lt;b&gt;珍贵&lt;/b&gt;&lt;/color&gt;  随机获得3张罕见礼物牌</t>
+    <t>随机获得3张罕见礼物牌</t>
   </si>
   <si>
     <t>商场里售卖的盲盒，不知道里面会开出什么东西</t>
@@ -1475,7 +1449,7 @@
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
     </row>
-    <row r="2" ht="28" spans="1:23">
+    <row r="2" ht="17.5" spans="1:23">
       <c r="A2" s="4">
         <v>11601</v>
       </c>
@@ -1494,14 +1468,12 @@
       <c r="F2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="6"/>
+      <c r="H2" s="7">
+        <v>4</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="H2" s="7">
-        <v>4</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4">
@@ -1525,12 +1497,12 @@
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
     </row>
-    <row r="3" ht="28" spans="1:23">
+    <row r="3" ht="15" spans="1:23">
       <c r="A3" s="4">
         <v>11602</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>22</v>
+      <c r="B3" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
@@ -1542,16 +1514,14 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="8"/>
+      <c r="H3" s="4">
+        <v>4</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="4">
-        <v>4</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4">
@@ -1580,7 +1550,7 @@
         <v>11001</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1595,7 +1565,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H4" s="4">
         <v>4</v>
@@ -1612,12 +1582,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="28" spans="1:23">
+    <row r="5" ht="15" spans="1:23">
       <c r="A5">
         <v>11002</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1629,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H5" s="7">
         <v>4</v>
@@ -1653,22 +1623,22 @@
         <v>11003</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="H6" s="4">
         <v>4</v>
@@ -1689,7 +1659,7 @@
         <v>11004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1701,10 +1671,10 @@
         <v>16</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H7" s="4">
         <v>4</v>
@@ -1720,12 +1690,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="42" spans="1:23">
+    <row r="8" ht="28" spans="1:23">
       <c r="A8">
         <v>11005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -1737,16 +1707,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="7">
+        <v>4</v>
+      </c>
+      <c r="I8" t="s">
         <v>37</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="7">
-        <v>4</v>
-      </c>
-      <c r="I8" t="s">
-        <v>39</v>
       </c>
       <c r="K8">
         <v>20</v>
@@ -1759,12 +1729,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" ht="42" spans="1:23">
+    <row r="9" ht="28" spans="1:23">
       <c r="A9">
         <v>11006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1776,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H9" s="9">
         <v>4</v>
@@ -1794,12 +1764,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" ht="28" spans="1:23">
+    <row r="10" ht="15" spans="1:23">
       <c r="A10">
         <v>12001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1811,16 +1781,16 @@
         <v>2</v>
       </c>
       <c r="F10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="9">
+        <v>4</v>
+      </c>
+      <c r="I10" t="s">
         <v>44</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="9">
-        <v>4</v>
-      </c>
-      <c r="I10" t="s">
-        <v>46</v>
       </c>
       <c r="K10">
         <v>40</v>
@@ -1833,12 +1803,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" ht="42" spans="1:23">
+    <row r="11" ht="28" spans="1:23">
       <c r="A11">
         <v>12002</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -1850,16 +1820,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="7">
+        <v>4</v>
+      </c>
+      <c r="I11" t="s">
         <v>48</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="7">
-        <v>4</v>
-      </c>
-      <c r="I11" t="s">
-        <v>50</v>
       </c>
       <c r="K11">
         <v>40</v>
@@ -1872,12 +1842,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="28" spans="1:23">
+    <row r="12" ht="17.5" spans="1:23">
       <c r="A12">
         <v>12003</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1889,16 +1859,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H12" s="9">
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K12">
         <v>40</v>
@@ -1911,12 +1881,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" ht="42" spans="1:23">
+    <row r="13" ht="28" spans="1:23">
       <c r="A13">
         <v>12004</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C13">
         <v>24</v>
@@ -1928,16 +1898,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H13" s="9">
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K13">
         <v>40</v>
@@ -1950,12 +1920,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="42" spans="1:23">
+    <row r="14" ht="28" spans="1:23">
       <c r="A14">
         <v>12005</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1967,16 +1937,16 @@
         <v>0</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H14" s="7">
         <v>4</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K14">
         <v>40</v>
@@ -1994,7 +1964,7 @@
         <v>12006</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2006,16 +1976,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H15" s="9">
         <v>4</v>
       </c>
       <c r="I15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K15">
         <v>40</v>
@@ -2025,7 +1995,7 @@
         <v>32</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="R15" s="4">
         <v>15</v>
@@ -2036,7 +2006,7 @@
         <v>12007</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2048,10 +2018,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H16" s="9">
         <v>4</v>
@@ -2064,7 +2034,7 @@
         <v>32</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -2075,7 +2045,7 @@
         <v>12008</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C17">
         <v>12</v>
@@ -2087,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H17" s="7">
         <v>4</v>
@@ -2103,18 +2073,18 @@
         <v>32</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="R17" s="4">
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="42" spans="1:18">
+    <row r="18" ht="28" spans="1:18">
       <c r="A18">
         <v>12009</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>40</v>
@@ -2126,16 +2096,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H18" s="9">
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K18">
         <v>40</v>
@@ -2148,12 +2118,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" ht="56" spans="1:18">
+    <row r="19" ht="28" spans="1:18">
       <c r="A19">
         <v>12010</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2165,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H19" s="9">
         <v>4</v>
@@ -2181,18 +2151,18 @@
         <v>32</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="R19">
         <v>10</v>
       </c>
     </row>
-    <row r="20" ht="42" spans="1:18">
+    <row r="20" ht="28" spans="1:18">
       <c r="A20">
         <v>12011</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -2204,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H20" s="7">
         <v>4</v>
@@ -2220,39 +2190,39 @@
         <v>32</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="R20" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="28" spans="1:18">
+    <row r="21" s="1" customFormat="1" ht="17.5" spans="1:18">
       <c r="A21" s="1">
         <v>13001</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="9">
+        <v>4</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="H21" s="9">
-        <v>4</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="K21" s="1">
         <v>80</v>
@@ -2274,7 +2244,7 @@
         <v>13002</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C22">
         <v>30</v>
@@ -2286,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H22"/>
       <c r="K22">
@@ -2300,7 +2270,7 @@
         <v>64</v>
       </c>
       <c r="M22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:18">
@@ -2308,7 +2278,7 @@
         <v>13003</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2320,13 +2290,13 @@
         <v>0</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K23" s="15">
         <v>80</v>
@@ -2341,7 +2311,7 @@
         <v>13004</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2353,10 +2323,10 @@
         <v>1</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="K24">
         <v>80</v>
@@ -2366,7 +2336,7 @@
         <v>64</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" ht="70" spans="1:18">
@@ -2374,7 +2344,7 @@
         <v>13005</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -2386,10 +2356,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K25" s="15">
         <v>80</v>
@@ -2399,7 +2369,7 @@
         <v>64</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" customFormat="1" ht="42" spans="1:18">
@@ -2407,25 +2377,25 @@
         <v>13006</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="N26" s="1">
         <v>80</v>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -2394,8 +2394,15 @@
       <c r="G26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L26" s="3" t="s">
+      <c r="I26" t="s">
         <v>105</v>
+      </c>
+      <c r="K26">
+        <v>80</v>
+      </c>
+      <c r="L26" s="2">
+        <f>K26*0.8</f>
+        <v>64</v>
       </c>
       <c r="N26" s="1">
         <v>80</v>

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -91,6 +91,9 @@
     <t>提升蒂娜的好感一{nature1}点</t>
   </si>
   <si>
+    <t>林奈第一次送给蒂娜的礼物，使用的是蓝色折纸</t>
+  </si>
+  <si>
     <t>shake(1,0.2)</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
   </si>
   <si>
     <t>提升蒂娜的好感二{nature2}点</t>
+  </si>
+  <si>
+    <t>林奈第一次送给蒂娜的礼物，使用的是黄色折纸</t>
   </si>
   <si>
     <t>magnify(0.2)</t>
@@ -216,13 +222,7 @@
     </r>
   </si>
   <si>
-    <t>提升蒂娜的好感一{nature1}点，当此牌被剪枝时，不会被消耗</t>
-  </si>
-  <si>
     <t>整颗冻干蓝莓外面裹着白巧克力，酸甜融合，蒂娜肯定会很喜欢</t>
-  </si>
-  <si>
-    <t>noConsumed()</t>
   </si>
   <si>
     <t>魔法少女变身器</t>
@@ -387,7 +387,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -400,7 +400,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF0F1115"/>
-      <name val="宋体"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1035,9 +1035,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1049,6 +1046,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1449,7 +1449,7 @@
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
     </row>
-    <row r="2" ht="17.5" spans="1:23">
+    <row r="2" ht="15" spans="1:23">
       <c r="A2" s="4">
         <v>11601</v>
       </c>
@@ -1468,12 +1468,14 @@
       <c r="F2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="6"/>
+      <c r="G2" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="H2" s="7">
         <v>4</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4">
@@ -1501,8 +1503,8 @@
       <c r="A3" s="4">
         <v>11602</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>21</v>
+      <c r="B3" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C3" s="4">
         <v>0</v>
@@ -1514,21 +1516,23 @@
         <v>0</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="H3" s="4">
         <v>4</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>23</v>
+      <c r="I3" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4">
         <v>10</v>
       </c>
       <c r="L3" s="2">
-        <f t="shared" ref="L3:L25" si="0">K3*0.8</f>
+        <f t="shared" ref="L3:L26" si="0">K3*0.8</f>
         <v>8</v>
       </c>
       <c r="M3" s="2"/>
@@ -1549,8 +1553,8 @@
       <c r="A4">
         <v>11001</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>24</v>
+      <c r="B4" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="C4">
         <v>8</v>
@@ -1561,16 +1565,16 @@
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>25</v>
+      <c r="G4" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="H4" s="4">
         <v>4</v>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="8"/>
       <c r="K4">
         <v>20</v>
       </c>
@@ -1586,8 +1590,8 @@
       <c r="A5">
         <v>11002</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>26</v>
+      <c r="B5" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1598,11 +1602,11 @@
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>27</v>
+      <c r="F5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="H5" s="7">
         <v>4</v>
@@ -1622,8 +1626,8 @@
       <c r="A6">
         <v>11003</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>28</v>
+      <c r="B6" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1634,11 +1638,11 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>30</v>
+      <c r="F6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="H6" s="4">
         <v>4</v>
@@ -1659,7 +1663,7 @@
         <v>11004</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1670,11 +1674,11 @@
       <c r="E7">
         <v>16</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>33</v>
+      <c r="F7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="H7" s="4">
         <v>4</v>
@@ -1695,7 +1699,7 @@
         <v>11005</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -1706,17 +1710,17 @@
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>36</v>
+      <c r="F8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="H8" s="7">
         <v>4</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K8">
         <v>20</v>
@@ -1734,7 +1738,7 @@
         <v>11006</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1745,13 +1749,13 @@
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="F9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="8">
         <v>4</v>
       </c>
       <c r="K9">
@@ -1768,8 +1772,8 @@
       <c r="A10">
         <v>12001</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>41</v>
+      <c r="B10" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1780,17 +1784,17 @@
       <c r="E10">
         <v>2</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="9">
+      <c r="F10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="8">
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K10">
         <v>40</v>
@@ -1807,8 +1811,8 @@
       <c r="A11">
         <v>12002</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>45</v>
+      <c r="B11" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -1819,17 +1823,17 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>47</v>
+      <c r="F11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="H11" s="7">
         <v>4</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K11">
         <v>40</v>
@@ -1846,8 +1850,8 @@
       <c r="A12">
         <v>12003</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>49</v>
+      <c r="B12" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1858,17 +1862,17 @@
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="9">
+      <c r="F12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="8">
         <v>4</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K12">
         <v>40</v>
@@ -1885,8 +1889,8 @@
       <c r="A13">
         <v>12004</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>51</v>
+      <c r="B13" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="C13">
         <v>24</v>
@@ -1897,17 +1901,17 @@
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="F13" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="8">
         <v>4</v>
       </c>
       <c r="I13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K13">
         <v>40</v>
@@ -1920,15 +1924,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" ht="28" spans="1:23">
+    <row r="14" ht="17.5" spans="1:23">
       <c r="A14">
         <v>12005</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>55</v>
+      <c r="B14" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1936,18 +1940,16 @@
       <c r="E14">
         <v>0</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>57</v>
+      <c r="F14" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="H14" s="7">
         <v>4</v>
       </c>
-      <c r="I14" t="s">
-        <v>58</v>
-      </c>
+      <c r="I14"/>
       <c r="K14">
         <v>40</v>
       </c>
@@ -1963,7 +1965,7 @@
       <c r="A15">
         <v>12006</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C15">
@@ -1975,13 +1977,13 @@
       <c r="E15">
         <v>0</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="8">
         <v>4</v>
       </c>
       <c r="I15" t="s">
@@ -2005,7 +2007,7 @@
       <c r="A16">
         <v>12007</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="12" t="s">
         <v>64</v>
       </c>
       <c r="C16">
@@ -2017,13 +2019,13 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="8">
         <v>4</v>
       </c>
       <c r="K16">
@@ -2044,7 +2046,7 @@
       <c r="A17">
         <v>12008</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="12" t="s">
         <v>68</v>
       </c>
       <c r="C17">
@@ -2056,10 +2058,10 @@
       <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="6" t="s">
         <v>70</v>
       </c>
       <c r="H17" s="7">
@@ -2083,7 +2085,7 @@
       <c r="A18">
         <v>12009</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="12" t="s">
         <v>72</v>
       </c>
       <c r="C18">
@@ -2095,13 +2097,13 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
         <v>4</v>
       </c>
       <c r="I18" t="s">
@@ -2122,7 +2124,7 @@
       <c r="A19">
         <v>12010</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="12" t="s">
         <v>76</v>
       </c>
       <c r="C19">
@@ -2134,13 +2136,13 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="8">
         <v>4</v>
       </c>
       <c r="K19">
@@ -2161,7 +2163,7 @@
       <c r="A20">
         <v>12011</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C20">
@@ -2173,10 +2175,10 @@
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>82</v>
       </c>
       <c r="H20" s="7">
@@ -2200,7 +2202,7 @@
       <c r="A21" s="1">
         <v>13001</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="12" t="s">
         <v>84</v>
       </c>
       <c r="C21" s="1">
@@ -2215,10 +2217,10 @@
       <c r="F21" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="8">
         <v>4</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -2243,7 +2245,7 @@
       <c r="A22" s="1">
         <v>13002</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C22">
@@ -2258,7 +2260,7 @@
       <c r="F22" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="12" t="s">
         <v>90</v>
       </c>
       <c r="H22"/>
@@ -2284,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2292,11 +2294,8 @@
       <c r="F23" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="I23" t="s">
-        <v>58</v>
       </c>
       <c r="K23" s="15">
         <v>80</v>
@@ -2325,7 +2324,7 @@
       <c r="F24" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="10" t="s">
         <v>96</v>
       </c>
       <c r="K24">
@@ -2358,7 +2357,7 @@
       <c r="F25" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="10" t="s">
         <v>100</v>
       </c>
       <c r="K25" s="15">
@@ -2401,7 +2400,7 @@
         <v>80</v>
       </c>
       <c r="L26" s="2">
-        <f>K26*0.8</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="N26" s="1">

--- a/giftCard.xlsx
+++ b/giftCard.xlsx
@@ -1949,7 +1949,6 @@
       <c r="H14" s="7">
         <v>4</v>
       </c>
-      <c r="I14"/>
       <c r="K14">
         <v>40</v>
       </c>
